--- a/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
+++ b/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
@@ -1927,25 +1927,22 @@
         <v>6.41</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.03</v>
+        <v>7.08</v>
       </c>
       <c r="AU8" t="n">
         <v>1.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>SHORT OF TARGET (22 vs 8)</t>
+          <t>KING WHITE PUSH — funded (22 → 8)</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $6.03, no premium — push conditions missing: velocity</t>
+          <t>top of search 6.41 → 7.08 this write (target 7.08, market bound); base 1.88 held; budget $54 → $73/day; read 2026-10-05, checkpoint 2026-10-12</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2303,16 +2300,13 @@
         <v>4.97</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.97</v>
+        <v>4.96</v>
       </c>
       <c r="AU10" t="n">
         <v>1.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>231</v>
+        <v>313</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -2321,7 +2315,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>distribution fix first and only: cut the base, re-solve the modifier to hold the top-of-search price; no climb, no budget move</t>
+          <t>distribution fix first: base 1.60 → 1.20, top of search held at 4.96 (queued for the King push, so not descended); push entry when top of search carries ≥70% of clicks for 7 days</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2331,7 +2325,7 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>RUN PRICE: the run takes top of search 4.96 → 4.97; the framework read gives 3.97 | SEARCH TERM: “bamboo sheets king size” — 12 of its 162 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (10), bamboo sheets california king-[Bamboo|Ca (1), Bamboo Sheets-(VHSV)-Broad-(DISC)-DO-BAM (1)</t>
+          <t>SEARCH TERM: “bamboo sheets king size” — 12 of its 162 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (10), bamboo sheets california king-[Bamboo|Ca (1), Bamboo Sheets-(VHSV)-Broad-(DISC)-DO-BAM (1)</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">

--- a/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
+++ b/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
@@ -4486,7 +4486,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days))</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
+          <t>advertise BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-WHITE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days)) | RUN PRICE: the run takes top of search 7.51 → 7.48; the framework read gives 3.75 | SEARCH TERM: “twin cooling sheets” — 7 of its 24 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (7)</t>
+          <t>RUN PRICE: the run takes top of search 7.51 → 7.48; the framework read gives 3.75 | SEARCH TERM: “twin cooling sheets” — 7 of its 24 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (7)</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE | negative-exact “twin cooling sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
+          <t>negative-exact “twin cooling sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days)) | RUN: swaps this campaign BAMBOO-TWIN-WHITE → BAMBOO-TWIN-BURGUNDY-NEW; the ranking SKU for the size is BAMBOO-TWIN-NAVYBLUE | SEARCH TERM: “bamboo sheets twin” — 4 of its 25 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (4)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE | RUN: swaps this campaign BAMBOO-TWIN-WHITE → BAMBOO-TWIN-BURGUNDY-NEW; the ranking SKU for the size is BAMBOO-TWIN-WHITE | SEARCH TERM: “bamboo sheets twin” — 4 of its 25 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (4)</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE | negative-exact “bamboo sheets twin” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
+          <t>advertise BAMBOO-TWIN-WHITE | negative-exact “bamboo sheets twin” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days)) | SEARCH TERM: “twin bamboo sheets” — 3 of its 41 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (3)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE | SEARCH TERM: “twin bamboo sheets” — 3 of its 41 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (3)</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE | negative-exact “twin bamboo sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
+          <t>advertise BAMBOO-TWIN-WHITE | negative-exact “twin bamboo sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
         </is>
       </c>
     </row>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -23947,12 +23947,12 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days))</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
+          <t>advertise BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
     </row>
@@ -24340,7 +24340,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -24464,12 +24464,12 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days))</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
+          <t>advertise BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
     </row>
@@ -34285,7 +34285,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -34379,12 +34379,12 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days))</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
+          <t>advertise BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
     </row>
@@ -34426,7 +34426,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -34520,12 +34520,12 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has none available until 16 Oct; Navy Blue is the next seller with healthy stock (81 days))</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
+          <t>advertise BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
     </row>
@@ -43102,7 +43102,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -44131,7 +44131,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -44571,7 +44571,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -44675,7 +44675,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -45383,7 +45383,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -45491,7 +45491,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-NAVYBLUE</t>
+          <t>BAMBOO-TWIN-WHITE</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>

--- a/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
+++ b/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN PRICE: the run takes top of search 6.69 → 8.37; the framework read gives 6.04 | SEARCH TERM: “bamboo sheets queen size” — 52 of its 194 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (25), bamboo sheets queen size-[Bamboo|Queen]- (19), 100 Bamboo-(VLSV)-Broad-(Discovery)-DO-B (5)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN PRICE: the run takes top of search 6.69 → 8.37; the framework read gives 6.04 | SEARCH TERM: “bamboo sheets queen size” — 52 of its 194 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (25), bamboo sheets queen size-[Bamboo|Queen]- (19), 100 Bamboo-(VLSV)-Broad-(Discovery)-DO-B (5)</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | SEARCH TERM: “bamboo sheets queen” — 7 of its 215 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (7)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | SEARCH TERM: “bamboo sheets queen” — 7 of its 215 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (7)</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN PRICE: the run takes top of search 7.61 → 8.26; the framework read gives 3.80 | SEARCH TERM: “bamboo cooling sheets” — 18 of its 109 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (16), bamboo sheets queen size-[Bamboo|Queen]- (2)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN PRICE: the run takes top of search 7.61 → 8.26; the framework read gives 3.80 | SEARCH TERM: “bamboo cooling sheets” — 18 of its 109 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (16), bamboo sheets queen size-[Bamboo|Queen]- (2)</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | SEARCH TERM: “cooling sheets queen” — 13 of its 171 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (10), 100 Bamboo-(VLSV)-Broad-(Discovery)-DO-B (2), Cooling Sheets-[Cooling]-(VHSV)-Broad-(R (1)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | SEARCH TERM: “cooling sheets queen” — 13 of its 171 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (10), 100 Bamboo-(VLSV)-Broad-(Discovery)-DO-B (2), Cooling Sheets-[Cooling]-(VHSV)-Broad-(R (1)</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | RUN PRICE: the run takes top of search 9.10 → 8.45; the framework read gives 4.55</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | RUN PRICE: the run takes top of search 9.10 → 8.45; the framework read gives 4.55</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
@@ -4414,26 +4414,14 @@
       <c r="AR22" t="n">
         <v>2.67</v>
       </c>
-      <c r="AS22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>124</v>
-      </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>NOT A RANKING CAMPAIGN IN PRACTICE — top of search 6%</t>
+          <t>STOCK THROTTLE — 0 available (0.0 days); 10 reserved are FC transfers</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>distribution fix first and only: cut the base, re-solve the modifier to hold the top-of-search price; no climb, no budget move</t>
+          <t>pause until the transfers show as Available</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -4441,11 +4429,7 @@
           <t>tos 86→147 | bid 1.43→1.08 | child BAMBOO-QUEEN-PURPLE→BAMBOO-FULL-PURPLE</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>RUN PRICE: the run takes top of search 2.66 → 2.67; the framework read gives 2.40</t>
-        </is>
-      </c>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -4486,7 +4470,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -4629,12 +4613,12 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White)</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
     </row>
@@ -5163,23 +5147,14 @@
       <c r="AR26" t="n">
         <v>2.03</v>
       </c>
-      <c r="AS26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>192</v>
-      </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>LEAKING — product pages 63%</t>
+          <t>STOCKOUT RISK — 0 available (0.0 days); reserved is customer orders or nothing</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>distribution fix: base toward the product-page ceiling, modifier re-solved so top of search holds</t>
+          <t>cut hard: stop advertising BAMBOO-FULL-WHITE; re-point to BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -5189,7 +5164,7 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-WHITE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days) | RUN: swaps this campaign BAMBOO-FULL-WHITE → BAMBOO-FULL-LIGHTOLIVE; the ranking SKU for the size is BAMBOO-FULL-OLIVE | SEARCH TERM: “cooling sheets full” — 2 of its 21 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (1), DECOLURE - B4 - QUEEN OLIVE - PRIME CAMP (1)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-WHITE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available) | RUN: swaps this campaign BAMBOO-FULL-WHITE → BAMBOO-FULL-LIGHTOLIVE; the ranking SKU for the size is BAMBOO-FULL-OLIVE | SEARCH TERM: “cooling sheets full” — 2 of its 21 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (1), DECOLURE - B4 - QUEEN OLIVE - PRIME CAMP (1)</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -5236,7 +5211,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -5353,26 +5328,14 @@
       <c r="AR27" t="n">
         <v>7.48</v>
       </c>
-      <c r="AS27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>297</v>
-      </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>LEAKING — product pages 62%</t>
+          <t>STOCK THROTTLE — 0 available (0.0 days); 154 reserved are FC transfers</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>distribution fix: base toward the product-page ceiling, modifier re-solved so top of search holds</t>
+          <t>stop advertising BAMBOO-TWIN-WHITE here; re-point to BAMBOO-TWIN-NAVYBLUE, which has Available stock; back to BAMBOO-TWIN-WHITE once the transfers show as Available</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -5382,12 +5345,12 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>RUN PRICE: the run takes top of search 7.51 → 7.48; the framework read gives 3.75 | SEARCH TERM: “twin cooling sheets” — 7 of its 24 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (7)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-WHITE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White) | SEARCH TERM: “twin cooling sheets” — 7 of its 24 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (7)</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>negative-exact “twin cooling sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE | negative-exact “twin cooling sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5727,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -5904,12 +5867,12 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE | RUN: swaps this campaign BAMBOO-TWIN-WHITE → BAMBOO-TWIN-BURGUNDY-NEW; the ranking SKU for the size is BAMBOO-TWIN-WHITE | SEARCH TERM: “bamboo sheets twin” — 4 of its 25 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (4)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White) | RUN: swaps this campaign BAMBOO-TWIN-WHITE → BAMBOO-TWIN-BURGUNDY-NEW; the ranking SKU for the size is BAMBOO-TWIN-NAVYBLUE | SEARCH TERM: “bamboo sheets twin” — 4 of its 25 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (4)</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE | negative-exact “bamboo sheets twin” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE | negative-exact “bamboo sheets twin” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6100,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -6277,12 +6240,12 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE | SEARCH TERM: “twin bamboo sheets” — 3 of its 41 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (3)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White) | SEARCH TERM: “twin bamboo sheets” — 3 of its 41 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (3)</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE | negative-exact “twin bamboo sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE | negative-exact “twin bamboo sheets” in LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6547,7 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | SEARCH TERM: “bamboo deep pocket queen sheets” — 1 of its 12 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (1)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | SEARCH TERM: “bamboo deep pocket queen sheets” — 1 of its 12 clicks (30d) go to LTSF-ALL-Broad-(Clearance)-DO-AGED-ALL (1)</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -9125,7 +9088,7 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
@@ -11636,7 +11599,7 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN PRICE: the run takes top of search 4.99 → 5.54; the framework read gives 4.99</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN PRICE: the run takes top of search 4.99 → 5.54; the framework read gives 4.99</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
@@ -12324,7 +12287,7 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
@@ -13356,7 +13319,7 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
@@ -14042,7 +14005,7 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN PRICE: the run takes top of search 2.67 → 2.96; the framework read gives 3.47</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN PRICE: the run takes top of search 2.67 → 2.96; the framework read gives 3.47</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
@@ -14411,7 +14374,7 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 7.3 top-of-search clicks/day; winning every auction at today’s volume would give ~2.3 — the requirement is above what the auction holds</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 7.3 top-of-search clicks/day; winning every auction at today’s volume would give ~2.3 — the requirement is above what the auction holds</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
@@ -16771,7 +16734,7 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
@@ -17284,7 +17247,7 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 14.7 top-of-search clicks/day; winning every auction at today’s volume would give ~6.5 — the requirement is above what the auction holds</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 14.7 top-of-search clicks/day; winning every auction at today’s volume would give ~6.5 — the requirement is above what the auction holds</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
@@ -17795,7 +17758,7 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
@@ -18492,7 +18455,7 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 5.3 top-of-search clicks/day; winning every auction at today’s volume would give ~1.4 — the requirement is above what the auction holds</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 5.3 top-of-search clicks/day; winning every auction at today’s volume would give ~1.4 — the requirement is above what the auction holds</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
@@ -19007,7 +18970,7 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | TRAFFIC: needs 5.3 top-of-search clicks/day; winning every auction at today’s volume would give ~2.0 — the requirement is above what the auction holds</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | TRAFFIC: needs 5.3 top-of-search clicks/day; winning every auction at today’s volume would give ~2.0 — the requirement is above what the auction holds</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
@@ -19191,7 +19154,7 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 6.1 top-of-search clicks/day; winning every auction at today’s volume would give ~2.0 — the requirement is above what the auction holds</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | TRAFFIC: needs 6.1 top-of-search clicks/day; winning every auction at today’s volume would give ~2.0 — the requirement is above what the auction holds</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
@@ -19540,7 +19503,7 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
@@ -19724,7 +19687,7 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
@@ -19893,7 +19856,7 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | KEYWORD: “cool sheets for hot sleepers” is also bought exact by DBS4-SP-Cooling Sheets For Hot Sleepers-[Cooling]-(LSV)-Exac — one owner per term; keep the one on the ranking SKU, pause the other</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | KEYWORD: “cool sheets for hot sleepers” is also bought exact by DBS4-SP-Cooling Sheets For Hot Sleepers-[Cooling]-(LSV)-Exac — one owner per term; keep the one on the ranking SKU, pause the other</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
@@ -20750,7 +20713,7 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
@@ -21104,7 +21067,7 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
@@ -21781,7 +21744,7 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
@@ -22939,7 +22902,7 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
@@ -23104,7 +23067,7 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
@@ -23581,23 +23544,14 @@
       <c r="AQ132" t="n">
         <v>2.61</v>
       </c>
-      <c r="AS132" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>161</v>
-      </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>LEAKING — product pages 29%</t>
+          <t>STOCKOUT RISK — 0 available (0.0 days); reserved is customer orders or nothing</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>distribution fix: base toward the product-page ceiling, modifier re-solved so top of search holds</t>
+          <t>cut hard: stop advertising BAMBOO-FULL-WHITE; re-point to BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -23607,7 +23561,7 @@
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-WHITE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days) | RUN: swaps this campaign BAMBOO-FULL-WHITE → BAMBOO-FULL-LIGHTOLIVE; the ranking SKU for the size is BAMBOO-FULL-OLIVE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-WHITE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available) | RUN: swaps this campaign BAMBOO-FULL-WHITE → BAMBOO-FULL-LIGHTOLIVE; the ranking SKU for the size is BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
@@ -23814,7 +23768,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -23947,12 +23901,12 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White)</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24247,7 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
@@ -24340,7 +24294,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -24464,12 +24418,12 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-BURGUNDY-NEW; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White)</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24595,7 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
@@ -25082,7 +25036,7 @@
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
@@ -25222,32 +25176,20 @@
       <c r="AQ142" t="n">
         <v>5.51</v>
       </c>
-      <c r="AS142" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AT142" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU142" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AV142" t="n">
-        <v>82</v>
-      </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>NO CLICKS — on, not delivering</t>
+          <t>STOCKOUT RISK — 0 available (0.0 days); reserved is customer orders or nothing</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>hold the base, move the modifier only (cutting the base of a row that is not delivering makes it worse)</t>
+          <t>cut hard: stop advertising BAMBOO-FULL-WHITE; re-point to BAMBOO-FULL-OLIVE</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-WHITE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-WHITE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
@@ -25687,7 +25629,7 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
@@ -25841,7 +25783,7 @@
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | ROS modifier 20% not earned (framework §8: 15+ rest-of-search clicks converting at or above product pages)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | ROS modifier 20% not earned (framework §8: 15+ rest-of-search clicks converting at or above product pages)</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
@@ -26417,7 +26359,7 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
@@ -26570,7 +26512,7 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
@@ -28468,7 +28410,7 @@
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
@@ -28766,7 +28708,7 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
@@ -28922,7 +28864,7 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
@@ -29525,7 +29467,7 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
@@ -29676,7 +29618,7 @@
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
@@ -30418,7 +30360,7 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
@@ -30735,7 +30677,7 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
@@ -30894,7 +30836,7 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
@@ -32456,7 +32398,7 @@
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
@@ -32601,7 +32543,7 @@
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
@@ -32746,7 +32688,7 @@
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
@@ -32899,7 +32841,7 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
@@ -33064,7 +33006,7 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
@@ -33638,7 +33580,7 @@
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | ROS modifier 20% not earned (framework §8: 15+ rest-of-search clicks converting at or above product pages)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE | ROS modifier 20% not earned (framework §8: 15+ rest-of-search clicks converting at or above product pages)</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
@@ -33940,7 +33882,7 @@
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
@@ -34093,7 +34035,7 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
@@ -34285,7 +34227,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -34379,12 +34321,12 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White)</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
     </row>
@@ -34426,7 +34368,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -34520,12 +34462,12 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-WHITE</t>
+          <t>SKU: ranking campaign advertises BAMBOO-TWIN-LIGHTBLUE; the size’s ranking SKU is BAMBOO-TWIN-NAVYBLUE (Twin White has 0 available — its 154 reserved are FC transfers, sellable in about 3–10 days; Navy Blue carries it (80 days available) until they show as Available, then back to White)</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>advertise BAMBOO-TWIN-WHITE</t>
+          <t>advertise BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
     </row>
@@ -34827,7 +34769,7 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
@@ -36253,7 +36195,7 @@
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | OBJECTIVE: the name says Ranking, the tag says Conversions | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | OBJECTIVE: the name says Ranking, the tag says Conversions | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
@@ -37093,7 +37035,7 @@
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | OBJECTIVE: the name says Ranking, the tag says Conversions | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | OBJECTIVE: the name says Ranking, the tag says Conversions | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
@@ -37232,7 +37174,7 @@
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
@@ -37756,7 +37698,7 @@
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
@@ -39251,7 +39193,7 @@
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
@@ -40322,7 +40264,7 @@
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
@@ -40572,7 +40514,7 @@
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
@@ -41120,7 +41062,7 @@
       <c r="AY257" t="inlineStr"/>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White is out until 27 Oct; Olive is the size’s top seller with 75 days)</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-FULL-LIGHTBLUE; the size’s ranking SKU is BAMBOO-FULL-OLIVE (Full White has 0 available; Olive is the size’s top seller with 70 days available)</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
@@ -41587,7 +41529,7 @@
       <c r="AY261" t="inlineStr"/>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
@@ -42142,7 +42084,7 @@
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days)</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-OLIVE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available)</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
@@ -42269,7 +42211,7 @@
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 23 days of cover against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 70 days) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
+          <t>OBJECTIVE: tagged Conversions but a Exact campaign is Ranking by the standard | SKU: ranking campaign advertises BAMBOO-QUEEN-WHITE; the size’s ranking SKU is BAMBOO-QUEEN-LIGHTBLUE (Queen White has 15 days Available against a 27 Oct arrival and sells on its own; Light Blue is the next seller with 57 days Available) | RUN: swaps this campaign BAMBOO-QUEEN-WHITE → BAMBOO-QUEEN-OLIVE; the ranking SKU for the size is BAMBOO-QUEEN-LIGHTBLUE</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
@@ -43102,7 +43044,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -44131,7 +44073,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -44571,7 +44513,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -44675,7 +44617,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -44729,12 +44671,12 @@
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>INSIDE ITS CEILING — ACoS 17%</t>
+          <t>STOCK THROTTLE — 0 available (0.0 days); 154 reserved are FC transfers</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>hold; nothing moves, including the top-of-search modifier</t>
+          <t>keep on a lower budget (branded / proven exact only)</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
@@ -45383,7 +45325,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -45491,7 +45433,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>BAMBOO-TWIN-WHITE</t>
+          <t>BAMBOO-TWIN-NAVYBLUE</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>

--- a/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
+++ b/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
@@ -823,7 +823,7 @@
         <v>3.422427518277668</v>
       </c>
       <c r="AI2" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.1266339869281046</v>
@@ -837,10 +837,10 @@
         <v>0.1104972375690608</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.87</v>
+        <v>3.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="AO2" t="n">
         <v>1.86</v>
@@ -852,16 +852,16 @@
         <v>7.42</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.87</v>
+        <v>3.71</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.87</v>
+        <v>3.61</v>
       </c>
       <c r="AU2" t="n">
         <v>1.86</v>
       </c>
       <c r="AV2" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $3.87, no premium — push conditions missing: velocity | budget capping (98% used, 7 days) — raise it before reading price; rates are truncated</t>
+          <t>maintenance: top of search at the ceiling $3.61, no premium — push conditions missing: velocity | budget capping (98% used, 7 days) — raise it before reading price; rates are truncated</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1898,7 +1898,7 @@
         <v>2.2543732213037</v>
       </c>
       <c r="AI8" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.1971830985915493</v>
@@ -1912,10 +1912,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM8" t="n">
-        <v>6.03</v>
+        <v>5.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1.88</v>
@@ -2081,7 +2081,7 @@
         <v>1.496332714020294</v>
       </c>
       <c r="AI9" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ9" t="n">
         <v>0.2105263157894737</v>
@@ -2095,10 +2095,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM9" t="n">
-        <v>6.45</v>
+        <v>6.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO9" t="n">
         <v>2.7</v>
@@ -2943,7 +2943,7 @@
         <v>25.03457142857143</v>
       </c>
       <c r="AI14" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ14" t="n">
         <v>0.209013011742304</v>
@@ -2957,10 +2957,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM14" t="n">
-        <v>6.39</v>
+        <v>5.96</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO14" t="n">
         <v>2.38</v>
@@ -2972,16 +2972,16 @@
         <v>9.76</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.39</v>
+        <v>5.96</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.39</v>
+        <v>5.96</v>
       </c>
       <c r="AU14" t="n">
         <v>2.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>12.42924170616114</v>
       </c>
       <c r="AI18" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ18" t="n">
         <v>0.1634275081643503</v>
@@ -3675,10 +3675,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM18" t="n">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="AN18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO18" t="n">
         <v>1.96</v>
@@ -3690,16 +3690,16 @@
         <v>8.27</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>4.66</v>
       </c>
       <c r="AU18" t="n">
         <v>1.96</v>
       </c>
       <c r="AV18" t="n">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.00, no premium — push conditions missing: velocity</t>
+          <t>maintenance: top of search at the ceiling $4.66, no premium — push conditions missing: velocity</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
         <v>7.800589595375722</v>
       </c>
       <c r="AI20" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ20" t="n">
         <v>0.1997681217864704</v>
@@ -4050,10 +4050,10 @@
         <v>0.09010761589403973</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.8</v>
+        <v>4.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AO20" t="n">
         <v>1.08</v>
@@ -4065,16 +4065,16 @@
         <v>6.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.8</v>
+        <v>4.06</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.8</v>
+        <v>4.06</v>
       </c>
       <c r="AU20" t="n">
         <v>1.08</v>
       </c>
       <c r="AV20" t="n">
-        <v>345</v>
+        <v>276</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.80, no premium — push conditions missing: velocity, ctr</t>
+          <t>maintenance: top of search at the ceiling $4.06, no premium — push conditions missing: velocity, ctr</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -4746,7 +4746,7 @@
         <v>10.46546365914787</v>
       </c>
       <c r="AI24" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ24" t="n">
         <v>0.1641414141414141</v>
@@ -4760,10 +4760,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO24" t="n">
         <v>1.81</v>
@@ -4775,16 +4775,16 @@
         <v>8.34</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT24" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU24" t="n">
         <v>1.81</v>
       </c>
       <c r="AV24" t="n">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, cvr</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -5475,7 +5475,7 @@
         <v>4.224558011049724</v>
       </c>
       <c r="AI28" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.1641414141414141</v>
@@ -5489,10 +5489,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO28" t="n">
         <v>1.5</v>
@@ -5504,16 +5504,16 @@
         <v>6.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU28" t="n">
         <v>1.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, cvr</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -5635,7 +5635,7 @@
         <v>7.80205</v>
       </c>
       <c r="AI29" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.1362935553499846</v>
@@ -5649,10 +5649,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM29" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN29" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO29" t="n">
         <v>1.57</v>
@@ -5664,16 +5664,16 @@
         <v>6.42</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU29" t="n">
         <v>1.57</v>
       </c>
       <c r="AV29" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>3.761211573236889</v>
       </c>
       <c r="AI30" t="n">
-        <v>46.54</v>
+        <v>18.41</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.1939255006798342</v>
@@ -5827,10 +5827,10 @@
         <v>0.05633802816901409</v>
       </c>
       <c r="AM30" t="n">
-        <v>9.029999999999999</v>
+        <v>3.57</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="AO30" t="n">
         <v>1.19</v>
@@ -6000,7 +6000,7 @@
         <v>12.48540041067762</v>
       </c>
       <c r="AI31" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.1362935553499846</v>
@@ -6014,10 +6014,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO31" t="n">
         <v>1.57</v>
@@ -6029,16 +6029,16 @@
         <v>4.79</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU31" t="n">
         <v>1.57</v>
       </c>
       <c r="AV31" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -6490,7 +6490,7 @@
         <v>5.139014306151645</v>
       </c>
       <c r="AI34" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ34" t="n">
         <v>0.1881390593047035</v>
@@ -6504,10 +6504,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM34" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO34" t="n">
         <v>2.09</v>
@@ -6519,16 +6519,16 @@
         <v>6.83</v>
       </c>
       <c r="AS34" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AU34" t="n">
         <v>1.67</v>
       </c>
       <c r="AV34" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>11.41321428571429</v>
       </c>
       <c r="AI36" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ36" t="n">
         <v>0.1362935553499846</v>
@@ -6868,10 +6868,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM36" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO36" t="n">
         <v>1.5</v>
@@ -6883,16 +6883,16 @@
         <v>5.08</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU36" t="n">
         <v>1.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -7040,7 +7040,7 @@
         <v>7.375916114790287</v>
       </c>
       <c r="AI37" t="n">
-        <v>35.16</v>
+        <v>26.64</v>
       </c>
       <c r="AJ37" t="n">
         <v>0.1362935553499846</v>
@@ -7054,10 +7054,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM37" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
       <c r="AN37" t="n">
-        <v>3.72</v>
+        <v>2.82</v>
       </c>
       <c r="AO37" t="n">
         <v>1.57</v>
@@ -7069,16 +7069,16 @@
         <v>4.98</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
       <c r="AU37" t="n">
         <v>1.57</v>
       </c>
       <c r="AV37" t="n">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.63, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -7598,7 +7598,7 @@
         <v>4.45264192139738</v>
       </c>
       <c r="AI40" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ40" t="n">
         <v>0.1678832116788321</v>
@@ -7612,10 +7612,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO40" t="n">
         <v>3</v>
@@ -7627,16 +7627,16 @@
         <v>5.37</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AU40" t="n">
         <v>3</v>
       </c>
       <c r="AV40" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.14, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -8135,7 +8135,7 @@
         <v>8.336096774193548</v>
       </c>
       <c r="AI43" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.1084695393759287</v>
@@ -8149,10 +8149,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM43" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN43" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO43" t="n">
         <v>3</v>
@@ -8164,16 +8164,16 @@
         <v>6</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AU43" t="n">
         <v>3</v>
       </c>
       <c r="AV43" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
         <v>15.94079245283019</v>
       </c>
       <c r="AI44" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ44" t="n">
         <v>0.1641414141414141</v>
@@ -8327,10 +8327,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM44" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN44" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO44" t="n">
         <v>1.96</v>
@@ -8342,16 +8342,16 @@
         <v>9.94</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU44" t="n">
         <v>1.96</v>
       </c>
       <c r="AV44" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
         <v>6.968549450549451</v>
       </c>
       <c r="AI45" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ45" t="n">
         <v>0.1362935553499846</v>
@@ -8513,10 +8513,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM45" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN45" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO45" t="n">
         <v>1.57</v>
@@ -8528,16 +8528,16 @@
         <v>4.79</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT45" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU45" t="n">
         <v>1.57</v>
       </c>
       <c r="AV45" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
         <v>19.68251028806585</v>
       </c>
       <c r="AI46" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ46" t="n">
         <v>0.1641414141414141</v>
@@ -8692,10 +8692,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN46" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO46" t="n">
         <v>1.96</v>
@@ -8707,16 +8707,16 @@
         <v>8.27</v>
       </c>
       <c r="AS46" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT46" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU46" t="n">
         <v>1.96</v>
       </c>
       <c r="AV46" t="n">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -9031,7 +9031,7 @@
         <v>20.26089552238806</v>
       </c>
       <c r="AI48" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ48" t="n">
         <v>0.1881390593047035</v>
@@ -9045,10 +9045,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM48" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN48" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO48" t="n">
         <v>2.7</v>
@@ -9060,16 +9060,16 @@
         <v>8.18</v>
       </c>
       <c r="AS48" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AU48" t="n">
         <v>2.7</v>
       </c>
       <c r="AV48" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.76, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.66, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -9221,7 +9221,7 @@
         <v>17.92900952380952</v>
       </c>
       <c r="AI49" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ49" t="n">
         <v>0.1516393442622951</v>
@@ -9235,10 +9235,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM49" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AO49" t="n">
         <v>2.8</v>
@@ -9250,16 +9250,16 @@
         <v>7.98</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AT49" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AU49" t="n">
         <v>2.8</v>
       </c>
       <c r="AV49" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.64, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.32, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -9400,7 +9400,7 @@
         <v>6.918905775075988</v>
       </c>
       <c r="AI50" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ50" t="n">
         <v>0.1362935553499846</v>
@@ -9414,10 +9414,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM50" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN50" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO50" t="n">
         <v>1.57</v>
@@ -9429,16 +9429,16 @@
         <v>4.98</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT50" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU50" t="n">
         <v>1.57</v>
       </c>
       <c r="AV50" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -9575,7 +9575,7 @@
         <v>3.197746478873239</v>
       </c>
       <c r="AI51" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ51" t="n">
         <v>0.1362935553499846</v>
@@ -9589,10 +9589,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM51" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN51" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO51" t="n">
         <v>1.57</v>
@@ -9604,16 +9604,16 @@
         <v>4.79</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT51" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU51" t="n">
         <v>1.57</v>
       </c>
       <c r="AV51" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -9738,7 +9738,7 @@
         <v>27.35325581395349</v>
       </c>
       <c r="AI52" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ52" t="n">
         <v>0.1641414141414141</v>
@@ -9752,10 +9752,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN52" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO52" t="n">
         <v>2.64</v>
@@ -9767,16 +9767,16 @@
         <v>9.640000000000001</v>
       </c>
       <c r="AS52" t="n">
-        <v>5.02</v>
+        <v>4.82</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU52" t="n">
         <v>2.64</v>
       </c>
       <c r="AV52" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>7.4624064171123</v>
       </c>
       <c r="AI53" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ53" t="n">
         <v>0.1641414141414141</v>
@@ -9930,10 +9930,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN53" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO53" t="n">
         <v>1.57</v>
@@ -9945,16 +9945,16 @@
         <v>5.1</v>
       </c>
       <c r="AS53" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT53" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU53" t="n">
         <v>1.57</v>
       </c>
       <c r="AV53" t="n">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -10095,7 +10095,7 @@
         <v>0.5115279770444764</v>
       </c>
       <c r="AI54" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ54" t="n">
         <v>0.1516393442622951</v>
@@ -10109,10 +10109,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM54" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AO54" t="n">
         <v>2.3</v>
@@ -10127,16 +10127,16 @@
         <v>12.07</v>
       </c>
       <c r="AS54" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AU54" t="n">
         <v>2.3</v>
       </c>
       <c r="AV54" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.64, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.32, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>ROS modifier 25% not earned (framework §8: 15+ rest-of-search clicks converting at or above product pages) | RUN PRICE: the run takes top of search 6.09 → 12.07; the framework read gives 4.64</t>
+          <t>ROS modifier 25% not earned (framework §8: 15+ rest-of-search clicks converting at or above product pages) | RUN PRICE: the run takes top of search 6.09 → 12.07; the framework read gives 4.32</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
@@ -10474,7 +10474,7 @@
         <v>9.205588235294117</v>
       </c>
       <c r="AI56" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ56" t="n">
         <v>0.1678832116788321</v>
@@ -10488,10 +10488,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN56" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO56" t="n">
         <v>2</v>
@@ -10503,13 +10503,16 @@
         <v>4.94</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>4.79</v>
       </c>
       <c r="AU56" t="n">
         <v>2</v>
       </c>
       <c r="AV56" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
@@ -10518,7 +10521,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.14, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -10653,7 +10656,7 @@
         <v>6.637121212121213</v>
       </c>
       <c r="AI57" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ57" t="n">
         <v>0.1881390593047035</v>
@@ -10667,10 +10670,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.77</v>
+        <v>5.4</v>
       </c>
       <c r="AN57" t="n">
-        <v>3.37</v>
+        <v>3.15</v>
       </c>
       <c r="AO57" t="n">
         <v>2.81</v>
@@ -10682,16 +10685,16 @@
         <v>10.09</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.77</v>
+        <v>5.4</v>
       </c>
       <c r="AT57" t="n">
-        <v>5.77</v>
+        <v>5.4</v>
       </c>
       <c r="AU57" t="n">
         <v>2.81</v>
       </c>
       <c r="AV57" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
@@ -10700,7 +10703,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.77, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.40, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -10843,7 +10846,7 @@
         <v>9.009850746268656</v>
       </c>
       <c r="AI58" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ58" t="n">
         <v>0.1641414141414141</v>
@@ -10857,10 +10860,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN58" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO58" t="n">
         <v>1.5</v>
@@ -10872,16 +10875,16 @@
         <v>6.42</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT58" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU58" t="n">
         <v>1.5</v>
       </c>
       <c r="AV58" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
@@ -10890,7 +10893,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -11714,7 +11717,7 @@
         <v>18.0266468489893</v>
       </c>
       <c r="AI63" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ63" t="n">
         <v>0.1362935553499846</v>
@@ -11728,10 +11731,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM63" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AN63" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AO63" t="n">
         <v>2.5</v>
@@ -11743,16 +11746,16 @@
         <v>6.17</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AT63" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AU63" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AV63" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
@@ -11885,7 +11888,7 @@
         <v>4.915963302752294</v>
       </c>
       <c r="AI64" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ64" t="n">
         <v>0.1880733944954129</v>
@@ -11899,10 +11902,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM64" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN64" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AO64" t="n">
         <v>2.5</v>
@@ -11914,16 +11917,16 @@
         <v>4.75</v>
       </c>
       <c r="AS64" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AT64" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AU64" t="n">
         <v>2.5</v>
       </c>
       <c r="AV64" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
@@ -12062,7 +12065,7 @@
         <v>2.170506329113924</v>
       </c>
       <c r="AI65" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ65" t="n">
         <v>0.1880733944954129</v>
@@ -12076,10 +12079,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM65" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN65" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AO65" t="n">
         <v>1.15</v>
@@ -12091,13 +12094,16 @@
         <v>4.35</v>
       </c>
       <c r="AS65" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>3.82</v>
       </c>
       <c r="AU65" t="n">
         <v>1.15</v>
       </c>
       <c r="AV65" t="n">
-        <v>293</v>
+        <v>232</v>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
@@ -12106,7 +12112,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.52, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.82, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -12234,7 +12240,7 @@
         <v>2.151743227326266</v>
       </c>
       <c r="AI66" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ66" t="n">
         <v>0.1686707566462168</v>
@@ -12248,10 +12254,10 @@
         <v>0.07706928264868179</v>
       </c>
       <c r="AM66" t="n">
-        <v>5.16</v>
+        <v>5.08</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AO66" t="n">
         <v>1.47</v>
@@ -12263,16 +12269,16 @@
         <v>5.48</v>
       </c>
       <c r="AS66" t="n">
-        <v>5.16</v>
+        <v>5.08</v>
       </c>
       <c r="AT66" t="n">
-        <v>5.16</v>
+        <v>5.08</v>
       </c>
       <c r="AU66" t="n">
         <v>1.1</v>
       </c>
       <c r="AV66" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
@@ -12420,7 +12426,7 @@
         <v>2.871467889908257</v>
       </c>
       <c r="AI67" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ67" t="n">
         <v>0.1362935553499846</v>
@@ -12434,10 +12440,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM67" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN67" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO67" t="n">
         <v>1.57</v>
@@ -12449,16 +12455,16 @@
         <v>5.1</v>
       </c>
       <c r="AS67" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT67" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU67" t="n">
         <v>1.57</v>
       </c>
       <c r="AV67" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
@@ -12467,7 +12473,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -12589,7 +12595,7 @@
         <v>8.155855855855856</v>
       </c>
       <c r="AI68" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ68" t="n">
         <v>0.1880733944954129</v>
@@ -12603,10 +12609,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM68" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN68" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AO68" t="n">
         <v>1.5</v>
@@ -12761,7 +12767,7 @@
         <v>7.037029702970298</v>
       </c>
       <c r="AI69" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ69" t="n">
         <v>0.1641414141414141</v>
@@ -12775,10 +12781,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM69" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN69" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO69" t="n">
         <v>1.57</v>
@@ -12790,16 +12796,16 @@
         <v>5.32</v>
       </c>
       <c r="AS69" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT69" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU69" t="n">
         <v>1.41</v>
       </c>
       <c r="AV69" t="n">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
@@ -12934,7 +12940,7 @@
         <v>2.721223854027592</v>
       </c>
       <c r="AI70" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ70" t="n">
         <v>0.1880733944954129</v>
@@ -12948,10 +12954,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM70" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN70" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AO70" t="n">
         <v>2.5</v>
@@ -12963,16 +12969,16 @@
         <v>4.75</v>
       </c>
       <c r="AS70" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AT70" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AU70" t="n">
         <v>2</v>
       </c>
       <c r="AV70" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
@@ -13265,7 +13271,7 @@
         <v>2.879662921348315</v>
       </c>
       <c r="AI72" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ72" t="n">
         <v>0.1948051948051948</v>
@@ -13279,10 +13285,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM72" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN72" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO72" t="n">
         <v>2</v>
@@ -13294,13 +13300,13 @@
         <v>4.94</v>
       </c>
       <c r="AS72" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AU72" t="n">
         <v>2</v>
       </c>
       <c r="AV72" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
@@ -13611,7 +13617,7 @@
         <v>12.21884780070066</v>
       </c>
       <c r="AI74" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ74" t="n">
         <v>0.1880733944954129</v>
@@ -13625,10 +13631,10 @@
         <v>0.1725165562913907</v>
       </c>
       <c r="AM74" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN74" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="AO74" t="n">
         <v>1.38</v>
@@ -13640,16 +13646,16 @@
         <v>5.56</v>
       </c>
       <c r="AS74" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AT74" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AU74" t="n">
         <v>1.03</v>
       </c>
       <c r="AV74" t="n">
-        <v>337</v>
+        <v>269</v>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
@@ -13791,7 +13797,7 @@
         <v>4.003977272727273</v>
       </c>
       <c r="AI75" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ75" t="n">
         <v>0.1678832116788321</v>
@@ -13805,10 +13811,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM75" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN75" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO75" t="n">
         <v>1.6</v>
@@ -13820,13 +13826,13 @@
         <v>3.9</v>
       </c>
       <c r="AS75" t="n">
-        <v>5.08</v>
+        <v>4.79</v>
       </c>
       <c r="AU75" t="n">
         <v>1.6</v>
       </c>
       <c r="AV75" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
@@ -13835,7 +13841,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.14, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -14135,7 +14141,7 @@
         <v>3.865098039215686</v>
       </c>
       <c r="AI77" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ77" t="n">
         <v>0.1362935553499846</v>
@@ -14149,10 +14155,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM77" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN77" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO77" t="n">
         <v>1.57</v>
@@ -14167,7 +14173,7 @@
         <v>4.17</v>
       </c>
       <c r="AT77" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU77" t="n">
         <v>1.57</v>
@@ -14182,7 +14188,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -14317,7 +14323,7 @@
         <v>3.09796875</v>
       </c>
       <c r="AI78" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ78" t="n">
         <v>0.1362935553499846</v>
@@ -14331,10 +14337,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM78" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN78" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO78" t="n">
         <v>1.32</v>
@@ -14346,16 +14352,16 @@
         <v>4.41</v>
       </c>
       <c r="AS78" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT78" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU78" t="n">
         <v>1.32</v>
       </c>
       <c r="AV78" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
@@ -14364,7 +14370,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.10, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -14486,7 +14492,7 @@
         <v>0.03296012615453931</v>
       </c>
       <c r="AI79" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ79" t="n">
         <v>0.1362935553499846</v>
@@ -14500,10 +14506,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM79" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN79" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO79" t="n">
         <v>1.43</v>
@@ -15016,7 +15022,7 @@
         <v>4.371428571428572</v>
       </c>
       <c r="AI82" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ82" t="n">
         <v>0.1678832116788321</v>
@@ -15030,10 +15036,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM82" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO82" t="n">
         <v>1.9</v>
@@ -15045,13 +15051,13 @@
         <v>4.69</v>
       </c>
       <c r="AS82" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AU82" t="n">
         <v>1.9</v>
       </c>
       <c r="AV82" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
@@ -15060,7 +15066,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.14, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -15189,7 +15195,7 @@
         <v>0.03815468940316687</v>
       </c>
       <c r="AI83" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ83" t="n">
         <v>0.203125</v>
@@ -15203,10 +15209,10 @@
         <v>0.1285714285714286</v>
       </c>
       <c r="AM83" t="n">
-        <v>6.23</v>
+        <v>5.83</v>
       </c>
       <c r="AN83" t="n">
-        <v>3.94</v>
+        <v>3.69</v>
       </c>
       <c r="AP83" t="n">
         <v>39</v>
@@ -15336,7 +15342,7 @@
         <v>15.96948051948052</v>
       </c>
       <c r="AI84" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ84" t="n">
         <v>0.1362935553499846</v>
@@ -15350,10 +15356,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM84" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AN84" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AO84" t="n">
         <v>2</v>
@@ -15365,16 +15371,16 @@
         <v>6.12</v>
       </c>
       <c r="AS84" t="n">
-        <v>3.28</v>
+        <v>3.06</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AU84" t="n">
         <v>2</v>
       </c>
       <c r="AV84" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
@@ -15519,7 +15525,7 @@
         <v>15.04817679558011</v>
       </c>
       <c r="AI85" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ85" t="n">
         <v>0.1362935553499846</v>
@@ -15533,10 +15539,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM85" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN85" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO85" t="n">
         <v>1.57</v>
@@ -15548,16 +15554,16 @@
         <v>4.79</v>
       </c>
       <c r="AS85" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT85" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU85" t="n">
         <v>1.57</v>
       </c>
       <c r="AV85" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
@@ -15566,7 +15572,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -15680,7 +15686,7 @@
         <v>21.66529411764706</v>
       </c>
       <c r="AI86" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ86" t="n">
         <v>0.1362935553499846</v>
@@ -15694,10 +15700,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM86" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN86" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO86" t="n">
         <v>2.5</v>
@@ -15709,16 +15715,16 @@
         <v>6.17</v>
       </c>
       <c r="AS86" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT86" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU86" t="n">
         <v>2.5</v>
       </c>
       <c r="AV86" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
@@ -15837,7 +15843,7 @@
         <v>0.7311111111111112</v>
       </c>
       <c r="AI87" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ87" t="n">
         <v>0.1362935553499846</v>
@@ -15851,10 +15857,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM87" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN87" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO87" t="n">
         <v>1.36</v>
@@ -16009,7 +16015,7 @@
         <v>1.281685823754789</v>
       </c>
       <c r="AI88" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ88" t="n">
         <v>0.1362935553499846</v>
@@ -16023,10 +16029,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM88" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN88" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO88" t="n">
         <v>1.2</v>
@@ -16038,13 +16044,13 @@
         <v>3.53</v>
       </c>
       <c r="AS88" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU88" t="n">
         <v>1.2</v>
       </c>
       <c r="AV88" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
@@ -16053,7 +16059,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -16173,7 +16179,7 @@
         <v>16.82777777777778</v>
       </c>
       <c r="AI89" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ89" t="n">
         <v>0.1641414141414141</v>
@@ -16187,10 +16193,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM89" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN89" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO89" t="n">
         <v>1.9</v>
@@ -16202,16 +16208,16 @@
         <v>7.73</v>
       </c>
       <c r="AS89" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT89" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU89" t="n">
         <v>1.9</v>
       </c>
       <c r="AV89" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
@@ -16522,7 +16528,7 @@
         <v>0.1011612903225806</v>
       </c>
       <c r="AI91" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ91" t="n">
         <v>0.1678832116788321</v>
@@ -16536,10 +16542,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM91" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN91" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO91" t="n">
         <v>0.95</v>
@@ -16695,7 +16701,7 @@
         <v>0.0649616368286445</v>
       </c>
       <c r="AI92" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ92" t="n">
         <v>0.1948051948051948</v>
@@ -16709,10 +16715,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM92" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN92" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AP92" t="n">
         <v>90</v>
@@ -16846,7 +16852,7 @@
         <v>0.3583908045977012</v>
       </c>
       <c r="AI93" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ93" t="n">
         <v>0.1362935553499846</v>
@@ -16860,10 +16866,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM93" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN93" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO93" t="n">
         <v>1.44</v>
@@ -16875,16 +16881,16 @@
         <v>4.87</v>
       </c>
       <c r="AS93" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT93" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU93" t="n">
         <v>1.15</v>
       </c>
       <c r="AV93" t="n">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
@@ -17021,7 +17027,7 @@
         <v>0.2401709401709402</v>
       </c>
       <c r="AI94" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ94" t="n">
         <v>0.1084695393759287</v>
@@ -17035,10 +17041,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM94" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN94" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO94" t="n">
         <v>1.35</v>
@@ -17190,7 +17196,7 @@
         <v>1.104005847953216</v>
       </c>
       <c r="AI95" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ95" t="n">
         <v>0.1362935553499846</v>
@@ -17204,10 +17210,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM95" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN95" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO95" t="n">
         <v>2</v>
@@ -17219,16 +17225,16 @@
         <v>4.94</v>
       </c>
       <c r="AS95" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT95" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU95" t="n">
         <v>2</v>
       </c>
       <c r="AV95" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
@@ -17237,7 +17243,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.10, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -17362,7 +17368,7 @@
         <v>17.3985</v>
       </c>
       <c r="AI96" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ96" t="n">
         <v>0.1362935553499846</v>
@@ -17376,10 +17382,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM96" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN96" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO96" t="n">
         <v>1.9</v>
@@ -17391,16 +17397,16 @@
         <v>4.69</v>
       </c>
       <c r="AS96" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT96" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU96" t="n">
         <v>1.9</v>
       </c>
       <c r="AV96" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
@@ -17537,7 +17543,7 @@
         <v>5.8559</v>
       </c>
       <c r="AI97" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ97" t="n">
         <v>0.1362935553499846</v>
@@ -17551,10 +17557,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM97" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN97" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO97" t="n">
         <v>1.5</v>
@@ -17566,16 +17572,16 @@
         <v>5.12</v>
       </c>
       <c r="AS97" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AT97" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AU97" t="n">
         <v>1.5</v>
       </c>
       <c r="AV97" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
@@ -17584,7 +17590,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.18, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.91, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -17705,7 +17711,7 @@
         <v>9.675192307692308</v>
       </c>
       <c r="AI98" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ98" t="n">
         <v>0.1881390593047035</v>
@@ -17719,10 +17725,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM98" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN98" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO98" t="n">
         <v>2.16</v>
@@ -17734,16 +17740,16 @@
         <v>8.210000000000001</v>
       </c>
       <c r="AS98" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AT98" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AU98" t="n">
         <v>2.16</v>
       </c>
       <c r="AV98" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
@@ -17885,7 +17891,7 @@
         <v>0.1717991631799163</v>
       </c>
       <c r="AI99" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ99" t="n">
         <v>0.154978354978355</v>
@@ -17899,10 +17905,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM99" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AN99" t="n">
-        <v>3.01</v>
+        <v>2.81</v>
       </c>
       <c r="AO99" t="n">
         <v>1.52</v>
@@ -17914,16 +17920,16 @@
         <v>4.92</v>
       </c>
       <c r="AS99" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AT99" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AU99" t="n">
         <v>1.52</v>
       </c>
       <c r="AV99" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
@@ -18053,7 +18059,7 @@
         <v>1.349161676646706</v>
       </c>
       <c r="AI100" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ100" t="n">
         <v>0.1276595744680851</v>
@@ -18067,10 +18073,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM100" t="n">
-        <v>3.92</v>
+        <v>3.66</v>
       </c>
       <c r="AN100" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO100" t="n">
         <v>1.9</v>
@@ -18082,13 +18088,13 @@
         <v>3.61</v>
       </c>
       <c r="AS100" t="n">
-        <v>3.92</v>
+        <v>3.66</v>
       </c>
       <c r="AU100" t="n">
         <v>1.9</v>
       </c>
       <c r="AV100" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
@@ -18218,7 +18224,7 @@
         <v>20.91569958847737</v>
       </c>
       <c r="AI101" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ101" t="n">
         <v>0.1481481481481481</v>
@@ -18232,10 +18238,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM101" t="n">
-        <v>4.53</v>
+        <v>4.23</v>
       </c>
       <c r="AN101" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO101" t="n">
         <v>1.33</v>
@@ -18247,13 +18253,13 @@
         <v>3.72</v>
       </c>
       <c r="AS101" t="n">
-        <v>4.53</v>
+        <v>4.23</v>
       </c>
       <c r="AU101" t="n">
         <v>1.33</v>
       </c>
       <c r="AV101" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
@@ -18398,7 +18404,7 @@
         <v>5.202105263157895</v>
       </c>
       <c r="AI102" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ102" t="n">
         <v>0.1881390593047035</v>
@@ -18412,10 +18418,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM102" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN102" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO102" t="n">
         <v>1.9</v>
@@ -18427,16 +18433,16 @@
         <v>6.29</v>
       </c>
       <c r="AS102" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AT102" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AU102" t="n">
         <v>1.9</v>
       </c>
       <c r="AV102" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
@@ -18445,7 +18451,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.76, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.66, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -18573,7 +18579,7 @@
         <v>4.179009900990099</v>
       </c>
       <c r="AI103" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ103" t="n">
         <v>0.1362935553499846</v>
@@ -18587,10 +18593,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM103" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN103" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO103" t="n">
         <v>1.9</v>
@@ -18602,16 +18608,16 @@
         <v>6.17</v>
       </c>
       <c r="AS103" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT103" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU103" t="n">
         <v>1.9</v>
       </c>
       <c r="AV103" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
@@ -18620,7 +18626,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -18734,7 +18740,7 @@
         <v>2.632236710130391</v>
       </c>
       <c r="AI104" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ104" t="n">
         <v>0.1362935553499846</v>
@@ -18748,10 +18754,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM104" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AN104" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AO104" t="n">
         <v>2</v>
@@ -18763,16 +18769,16 @@
         <v>3.8</v>
       </c>
       <c r="AS104" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AT104" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AU104" t="n">
         <v>1.8</v>
       </c>
       <c r="AV104" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
@@ -18917,7 +18923,7 @@
         <v>3.49825</v>
       </c>
       <c r="AI105" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ105" t="n">
         <v>0.1881390593047035</v>
@@ -18931,10 +18937,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM105" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN105" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO105" t="n">
         <v>1.9</v>
@@ -18946,16 +18952,16 @@
         <v>8.19</v>
       </c>
       <c r="AS105" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AT105" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AU105" t="n">
         <v>1.52</v>
       </c>
       <c r="AV105" t="n">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
@@ -19100,7 +19106,7 @@
         <v>3.529666666666667</v>
       </c>
       <c r="AI106" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ106" t="n">
         <v>0.1881390593047035</v>
@@ -19114,10 +19120,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM106" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN106" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO106" t="n">
         <v>1.5</v>
@@ -19129,13 +19135,13 @@
         <v>5.07</v>
       </c>
       <c r="AS106" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AU106" t="n">
         <v>1.5</v>
       </c>
       <c r="AV106" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
@@ -19144,7 +19150,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.76, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.66, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -19278,7 +19284,7 @@
         <v>7.090909090909091</v>
       </c>
       <c r="AI107" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ107" t="n">
         <v>0.141025641025641</v>
@@ -19292,10 +19298,10 @@
         <v>0.1311475409836066</v>
       </c>
       <c r="AM107" t="n">
-        <v>4.31</v>
+        <v>4.02</v>
       </c>
       <c r="AN107" t="n">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="AO107" t="n">
         <v>1.27</v>
@@ -19449,7 +19455,7 @@
         <v>0.3259030100334448</v>
       </c>
       <c r="AI108" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ108" t="n">
         <v>0.1948051948051948</v>
@@ -19463,10 +19469,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM108" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO108" t="n">
         <v>2</v>
@@ -19633,7 +19639,7 @@
         <v>2.914827586206897</v>
       </c>
       <c r="AI109" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ109" t="n">
         <v>0.1948051948051948</v>
@@ -19647,10 +19653,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM109" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN109" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO109" t="n">
         <v>2</v>
@@ -19802,7 +19808,7 @@
         <v>0</v>
       </c>
       <c r="AI110" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ110" t="n">
         <v>0.1084695393759287</v>
@@ -19816,10 +19822,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM110" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="AN110" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="AO110" t="n">
         <v>1.6</v>
@@ -19986,7 +19992,7 @@
         <v>0.3032191780821918</v>
       </c>
       <c r="AI111" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ111" t="n">
         <v>0.1678832116788321</v>
@@ -20000,10 +20006,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM111" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN111" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO111" t="n">
         <v>1.6</v>
@@ -20030,7 +20036,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.14, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -20149,7 +20155,7 @@
         <v>0.5663333333333332</v>
       </c>
       <c r="AI112" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ112" t="n">
         <v>0.1641414141414141</v>
@@ -20163,10 +20169,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM112" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN112" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO112" t="n">
         <v>1.45</v>
@@ -20178,13 +20184,16 @@
         <v>4.73</v>
       </c>
       <c r="AS112" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
+      </c>
+      <c r="AT112" t="n">
+        <v>4.68</v>
       </c>
       <c r="AU112" t="n">
         <v>1.45</v>
       </c>
       <c r="AV112" t="n">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
@@ -20193,7 +20202,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -20318,7 +20327,7 @@
         <v>2.432063492063492</v>
       </c>
       <c r="AI113" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ113" t="n">
         <v>0.1362935553499846</v>
@@ -20332,10 +20341,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM113" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN113" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO113" t="n">
         <v>2.25</v>
@@ -20347,16 +20356,16 @@
         <v>5.56</v>
       </c>
       <c r="AS113" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AT113" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AU113" t="n">
         <v>2.25</v>
       </c>
       <c r="AV113" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
@@ -20365,7 +20374,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.18, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.91, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -20501,7 +20510,7 @@
         <v>0.3667021276595744</v>
       </c>
       <c r="AI114" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ114" t="n">
         <v>0.1362935553499846</v>
@@ -20515,10 +20524,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM114" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN114" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO114" t="n">
         <v>1.57</v>
@@ -20659,7 +20668,7 @@
         <v>0.735736040609137</v>
       </c>
       <c r="AI115" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ115" t="n">
         <v>0.1948051948051948</v>
@@ -20673,10 +20682,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM115" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN115" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO115" t="n">
         <v>1.92</v>
@@ -20688,13 +20697,13 @@
         <v>4.74</v>
       </c>
       <c r="AS115" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AU115" t="n">
         <v>1.92</v>
       </c>
       <c r="AV115" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
@@ -21017,7 +21026,7 @@
         <v>0.02829652996845426</v>
       </c>
       <c r="AI117" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ117" t="n">
         <v>0.1488925080644966</v>
@@ -21031,10 +21040,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM117" t="n">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="AN117" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="AO117" t="n">
         <v>1.9</v>
@@ -21182,7 +21191,7 @@
         <v>0.7128225806451612</v>
       </c>
       <c r="AI118" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ118" t="n">
         <v>0.1362935553499846</v>
@@ -21196,10 +21205,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM118" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN118" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO118" t="n">
         <v>1.9</v>
@@ -21211,16 +21220,16 @@
         <v>5.81</v>
       </c>
       <c r="AS118" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT118" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU118" t="n">
         <v>1.9</v>
       </c>
       <c r="AV118" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
@@ -21345,7 +21354,7 @@
         <v>6.299545454545455</v>
       </c>
       <c r="AI119" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ119" t="n">
         <v>0.1362935553499846</v>
@@ -21359,10 +21368,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM119" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN119" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO119" t="n">
         <v>1.9</v>
@@ -21374,16 +21383,16 @@
         <v>4.52</v>
       </c>
       <c r="AS119" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AT119" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AU119" t="n">
         <v>1.9</v>
       </c>
       <c r="AV119" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
@@ -21525,7 +21534,7 @@
         <v>0.009510229386236826</v>
       </c>
       <c r="AI120" t="n">
-        <v>35.15</v>
+        <v>29.86</v>
       </c>
       <c r="AJ120" t="n">
         <v>0.1084695393759287</v>
@@ -21539,10 +21548,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM120" t="n">
-        <v>3.81</v>
+        <v>3.24</v>
       </c>
       <c r="AN120" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="AO120" t="n">
         <v>1.92</v>
@@ -21554,13 +21563,16 @@
         <v>3.61</v>
       </c>
       <c r="AS120" t="n">
-        <v>3.61</v>
+        <v>3.24</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>3.24</v>
       </c>
       <c r="AU120" t="n">
         <v>1.25</v>
       </c>
       <c r="AV120" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
@@ -21694,7 +21706,7 @@
         <v>2.01064</v>
       </c>
       <c r="AI121" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ121" t="n">
         <v>0.1362935553499846</v>
@@ -21708,10 +21720,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM121" t="n">
-        <v>3.84</v>
+        <v>3.27</v>
       </c>
       <c r="AN121" t="n">
-        <v>2.98</v>
+        <v>2.53</v>
       </c>
       <c r="AO121" t="n">
         <v>2</v>
@@ -21856,7 +21868,7 @@
         <v>0.2998275862068965</v>
       </c>
       <c r="AI122" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ122" t="n">
         <v>0.1678832116788321</v>
@@ -21870,10 +21882,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM122" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN122" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO122" t="n">
         <v>1.92</v>
@@ -21885,13 +21897,13 @@
         <v>3.71</v>
       </c>
       <c r="AS122" t="n">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="AU122" t="n">
         <v>1.92</v>
       </c>
       <c r="AV122" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
@@ -22029,7 +22041,7 @@
         <v>4.15102564102564</v>
       </c>
       <c r="AI123" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ123" t="n">
         <v>0.1641414141414141</v>
@@ -22043,10 +22055,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM123" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN123" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO123" t="n">
         <v>1.3</v>
@@ -22073,7 +22085,7 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -22198,7 +22210,7 @@
         <v>3.77</v>
       </c>
       <c r="AI124" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ124" t="n">
         <v>0.1362935553499846</v>
@@ -22212,10 +22224,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM124" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN124" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO124" t="n">
         <v>1.3</v>
@@ -22371,7 +22383,7 @@
         <v>0.02416918429003021</v>
       </c>
       <c r="AI125" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ125" t="n">
         <v>0.1754385964912281</v>
@@ -22385,10 +22397,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM125" t="n">
-        <v>5.37</v>
+        <v>5</v>
       </c>
       <c r="AN125" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO125" t="n">
         <v>1.9</v>
@@ -22403,10 +22415,10 @@
         <v>2.85</v>
       </c>
       <c r="AU125" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AV125" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
@@ -22525,7 +22537,7 @@
         <v>7.14</v>
       </c>
       <c r="AI126" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ126" t="n">
         <v>0.1362935553499846</v>
@@ -22539,10 +22551,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM126" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN126" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO126" t="n">
         <v>1.9</v>
@@ -22554,13 +22566,13 @@
         <v>3.59</v>
       </c>
       <c r="AS126" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AU126" t="n">
         <v>1.9</v>
       </c>
       <c r="AV126" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
@@ -22687,7 +22699,7 @@
         <v>1.565217391304348</v>
       </c>
       <c r="AI127" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ127" t="n">
         <v>0.1362935553499846</v>
@@ -22701,10 +22713,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM127" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN127" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO127" t="n">
         <v>1.9</v>
@@ -22716,13 +22728,13 @@
         <v>3.59</v>
       </c>
       <c r="AS127" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AU127" t="n">
         <v>1.9</v>
       </c>
       <c r="AV127" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
@@ -22849,7 +22861,7 @@
         <v>4.235405405405405</v>
       </c>
       <c r="AI128" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ128" t="n">
         <v>0.1362935553499846</v>
@@ -22863,10 +22875,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM128" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN128" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO128" t="n">
         <v>2.83</v>
@@ -22878,16 +22890,16 @@
         <v>5.38</v>
       </c>
       <c r="AS128" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT128" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU128" t="n">
         <v>2.12</v>
       </c>
       <c r="AV128" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
@@ -23017,7 +23029,7 @@
         <v>1.848484848484848</v>
       </c>
       <c r="AI129" t="n">
-        <v>34.87</v>
+        <v>27.58</v>
       </c>
       <c r="AJ129" t="n">
         <v>0.1881390593047035</v>
@@ -23031,10 +23043,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM129" t="n">
-        <v>6.56</v>
+        <v>5.19</v>
       </c>
       <c r="AN129" t="n">
-        <v>3.83</v>
+        <v>3.03</v>
       </c>
       <c r="AO129" t="n">
         <v>1.9</v>
@@ -23200,7 +23212,7 @@
         <v>0.4303937007874015</v>
       </c>
       <c r="AI130" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ130" t="n">
         <v>0.1880733944954129</v>
@@ -23214,10 +23226,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM130" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN130" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AO130" t="n">
         <v>0.96</v>
@@ -23354,7 +23366,7 @@
         <v>0.2833333333333333</v>
       </c>
       <c r="AI131" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ131" t="n">
         <v>0.1084695393759287</v>
@@ -23368,10 +23380,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM131" t="n">
-        <v>3.33</v>
+        <v>3.11</v>
       </c>
       <c r="AN131" t="n">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="AO131" t="n">
         <v>1.6</v>
@@ -23383,13 +23395,16 @@
         <v>3.22</v>
       </c>
       <c r="AS131" t="n">
-        <v>3.33</v>
+        <v>3.11</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>3.11</v>
       </c>
       <c r="AU131" t="n">
         <v>1.6</v>
       </c>
       <c r="AV131" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
@@ -23676,7 +23691,7 @@
         <v>12.17392857142857</v>
       </c>
       <c r="AI133" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ133" t="n">
         <v>0.1362935553499846</v>
@@ -23690,10 +23705,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM133" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN133" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO133" t="n">
         <v>2</v>
@@ -23705,16 +23720,16 @@
         <v>7.64</v>
       </c>
       <c r="AS133" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT133" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU133" t="n">
         <v>2</v>
       </c>
       <c r="AV133" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
@@ -23848,7 +23863,7 @@
         <v>0.06273469387755103</v>
       </c>
       <c r="AI134" t="n">
-        <v>24.37</v>
+        <v>21.71</v>
       </c>
       <c r="AJ134" t="n">
         <v>0.1362935553499846</v>
@@ -23862,10 +23877,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM134" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="AN134" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="AO134" t="n">
         <v>1.9</v>
@@ -23877,16 +23892,16 @@
         <v>4.69</v>
       </c>
       <c r="AS134" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="AT134" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="AU134" t="n">
         <v>1.52</v>
       </c>
       <c r="AV134" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
@@ -24013,7 +24028,7 @@
         <v>3.534791666666667</v>
       </c>
       <c r="AI135" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ135" t="n">
         <v>0.1362935553499846</v>
@@ -24027,10 +24042,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM135" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN135" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AO135" t="n">
         <v>1.9</v>
@@ -24042,16 +24057,16 @@
         <v>4.37</v>
       </c>
       <c r="AS135" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AT135" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AU135" t="n">
         <v>1.23</v>
       </c>
       <c r="AV135" t="n">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
@@ -24193,7 +24208,7 @@
         <v>0.09685855263157894</v>
       </c>
       <c r="AI136" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ136" t="n">
         <v>0.1807496004536784</v>
@@ -24207,10 +24222,10 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="AM136" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="AN136" t="n">
-        <v>4.08</v>
+        <v>4.01</v>
       </c>
       <c r="AO136" t="n">
         <v>1.43</v>
@@ -24368,7 +24383,7 @@
         <v>1.503013698630137</v>
       </c>
       <c r="AI137" t="n">
-        <v>46.54</v>
+        <v>18.41</v>
       </c>
       <c r="AJ137" t="n">
         <v>0.1477309301577084</v>
@@ -24382,10 +24397,10 @@
         <v>0.05633802816901409</v>
       </c>
       <c r="AM137" t="n">
-        <v>6.88</v>
+        <v>2.72</v>
       </c>
       <c r="AN137" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="AO137" t="n">
         <v>0.74</v>
@@ -24545,7 +24560,7 @@
         <v>0</v>
       </c>
       <c r="AI138" t="n">
-        <v>34.87</v>
+        <v>27.58</v>
       </c>
       <c r="AJ138" t="n">
         <v>0.1881390593047035</v>
@@ -24559,10 +24574,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM138" t="n">
-        <v>6.56</v>
+        <v>5.19</v>
       </c>
       <c r="AN138" t="n">
-        <v>3.83</v>
+        <v>3.03</v>
       </c>
       <c r="AO138" t="n">
         <v>0.45</v>
@@ -24707,7 +24722,7 @@
         <v>12.57789269553976</v>
       </c>
       <c r="AI139" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ139" t="n">
         <v>0.1362935553499846</v>
@@ -24721,10 +24736,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM139" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN139" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO139" t="n">
         <v>1.32</v>
@@ -24849,7 +24864,7 @@
         <v>0</v>
       </c>
       <c r="AI140" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ140" t="n">
         <v>0.1362935553499846</v>
@@ -24863,10 +24878,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM140" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN140" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO140" t="n">
         <v>1.9</v>
@@ -24997,7 +25012,7 @@
         <v>0</v>
       </c>
       <c r="AI141" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ141" t="n">
         <v>0.1516393442622951</v>
@@ -25011,10 +25026,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM141" t="n">
-        <v>4.64</v>
+        <v>4.56</v>
       </c>
       <c r="AN141" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AP141" t="n">
         <v>36</v>
@@ -25026,7 +25041,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.64, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.56, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -25286,7 +25301,7 @@
         </is>
       </c>
       <c r="AI143" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ143" t="n">
         <v>0.1362935553499846</v>
@@ -25300,10 +25315,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM143" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN143" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO143" t="n">
         <v>2.28</v>
@@ -25315,16 +25330,16 @@
         <v>5.4</v>
       </c>
       <c r="AS143" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT143" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU143" t="n">
         <v>2.28</v>
       </c>
       <c r="AV143" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
@@ -25431,7 +25446,7 @@
         <v>0.7595652173913043</v>
       </c>
       <c r="AI144" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ144" t="n">
         <v>0.1362935553499846</v>
@@ -25445,10 +25460,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM144" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN144" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO144" t="n">
         <v>2</v>
@@ -25460,16 +25475,16 @@
         <v>4.94</v>
       </c>
       <c r="AS144" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT144" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU144" t="n">
         <v>2</v>
       </c>
       <c r="AV144" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
@@ -25576,7 +25591,7 @@
         <v>0.4974626865671641</v>
       </c>
       <c r="AI145" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ145" t="n">
         <v>0.1362935553499846</v>
@@ -25590,10 +25605,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM145" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN145" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO145" t="n">
         <v>2.79</v>
@@ -25605,16 +25620,16 @@
         <v>5.27</v>
       </c>
       <c r="AS145" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT145" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU145" t="n">
         <v>2.79</v>
       </c>
       <c r="AV145" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
@@ -25729,7 +25744,7 @@
         <v>0</v>
       </c>
       <c r="AI146" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ146" t="n">
         <v>0.1362935553499846</v>
@@ -25743,10 +25758,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM146" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN146" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO146" t="n">
         <v>1.92</v>
@@ -25877,7 +25892,7 @@
         </is>
       </c>
       <c r="AI147" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ147" t="n">
         <v>0.1362935553499846</v>
@@ -25891,10 +25906,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM147" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN147" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO147" t="n">
         <v>1.9</v>
@@ -26019,7 +26034,7 @@
         <v>0</v>
       </c>
       <c r="AI148" t="n">
-        <v>35.16</v>
+        <v>26.64</v>
       </c>
       <c r="AJ148" t="n">
         <v>0.1362935553499846</v>
@@ -26033,10 +26048,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM148" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
       <c r="AN148" t="n">
-        <v>3.72</v>
+        <v>2.82</v>
       </c>
       <c r="AO148" t="n">
         <v>1.9</v>
@@ -26161,7 +26176,7 @@
         <v>1.741666666666667</v>
       </c>
       <c r="AI149" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ149" t="n">
         <v>0.1362935553499846</v>
@@ -26175,10 +26190,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM149" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN149" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO149" t="n">
         <v>2</v>
@@ -26190,16 +26205,16 @@
         <v>4.94</v>
       </c>
       <c r="AS149" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT149" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU149" t="n">
         <v>2</v>
       </c>
       <c r="AV149" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
@@ -26306,7 +26321,7 @@
         <v>6.260909090909092</v>
       </c>
       <c r="AI150" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ150" t="n">
         <v>0.1362935553499846</v>
@@ -26320,10 +26335,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM150" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN150" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO150" t="n">
         <v>1.9</v>
@@ -26335,16 +26350,16 @@
         <v>4.69</v>
       </c>
       <c r="AS150" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT150" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU150" t="n">
         <v>1.9</v>
       </c>
       <c r="AV150" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
@@ -26459,7 +26474,7 @@
         <v>6.580540540540541</v>
       </c>
       <c r="AI151" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ151" t="n">
         <v>0.1362935553499846</v>
@@ -26473,10 +26488,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM151" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN151" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO151" t="n">
         <v>2.28</v>
@@ -26488,16 +26503,16 @@
         <v>7.07</v>
       </c>
       <c r="AS151" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT151" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU151" t="n">
         <v>1.71</v>
       </c>
       <c r="AV151" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
@@ -26612,7 +26627,7 @@
         <v>4.613776595744681</v>
       </c>
       <c r="AI152" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ152" t="n">
         <v>0.1362935553499846</v>
@@ -26626,10 +26641,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM152" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN152" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO152" t="n">
         <v>2.23</v>
@@ -26641,16 +26656,16 @@
         <v>5.24</v>
       </c>
       <c r="AS152" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT152" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU152" t="n">
         <v>2.23</v>
       </c>
       <c r="AV152" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
@@ -26751,7 +26766,7 @@
         </is>
       </c>
       <c r="AI153" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ153" t="n">
         <v>0.1362935553499846</v>
@@ -26765,10 +26780,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM153" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN153" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO153" t="n">
         <v>1.9</v>
@@ -26884,7 +26899,7 @@
         </is>
       </c>
       <c r="AI154" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ154" t="n">
         <v>0.1362935553499846</v>
@@ -26898,10 +26913,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM154" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN154" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO154" t="n">
         <v>1.9</v>
@@ -26913,16 +26928,16 @@
         <v>4.46</v>
       </c>
       <c r="AS154" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT154" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU154" t="n">
         <v>1.9</v>
       </c>
       <c r="AV154" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
@@ -27041,7 +27056,7 @@
         <v>9.21917808219178</v>
       </c>
       <c r="AI155" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ155" t="n">
         <v>0.1084695393759287</v>
@@ -27055,10 +27070,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM155" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN155" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO155" t="n">
         <v>1.8</v>
@@ -27183,7 +27198,7 @@
         <v>0</v>
       </c>
       <c r="AI156" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ156" t="n">
         <v>0.1362935553499846</v>
@@ -27197,10 +27212,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM156" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN156" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO156" t="n">
         <v>2.28</v>
@@ -27334,7 +27349,7 @@
         <v>14.16294117647059</v>
       </c>
       <c r="AI157" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ157" t="n">
         <v>0.1641414141414141</v>
@@ -27348,10 +27363,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM157" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN157" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO157" t="n">
         <v>1.5</v>
@@ -27363,16 +27378,16 @@
         <v>5.78</v>
       </c>
       <c r="AS157" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AT157" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU157" t="n">
         <v>1.5</v>
       </c>
       <c r="AV157" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
@@ -27381,7 +27396,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -27491,7 +27506,7 @@
         <v>9.21917808219178</v>
       </c>
       <c r="AI158" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ158" t="n">
         <v>0.1084695393759287</v>
@@ -27505,10 +27520,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM158" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN158" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO158" t="n">
         <v>1.6</v>
@@ -27630,7 +27645,7 @@
         </is>
       </c>
       <c r="AI159" t="n">
-        <v>30.54</v>
+        <v>29.19</v>
       </c>
       <c r="AJ159" t="n">
         <v>0.1362935553499846</v>
@@ -27644,10 +27659,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM159" t="n">
-        <v>4.16</v>
+        <v>3.98</v>
       </c>
       <c r="AN159" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="AO159" t="n">
         <v>1.9</v>
@@ -27659,13 +27674,13 @@
         <v>3.1</v>
       </c>
       <c r="AS159" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="AU159" t="n">
         <v>1.9</v>
       </c>
       <c r="AV159" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
@@ -27772,7 +27787,7 @@
         <v>0</v>
       </c>
       <c r="AI160" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ160" t="n">
         <v>0.1362935553499846</v>
@@ -27786,10 +27801,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM160" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN160" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO160" t="n">
         <v>1.9</v>
@@ -27801,16 +27816,16 @@
         <v>4.69</v>
       </c>
       <c r="AS160" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT160" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU160" t="n">
         <v>1.52</v>
       </c>
       <c r="AV160" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
@@ -28205,7 +28220,7 @@
         <v>0</v>
       </c>
       <c r="AI163" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ163" t="n">
         <v>0.1362935553499846</v>
@@ -28219,10 +28234,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM163" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN163" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO163" t="n">
         <v>1.9</v>
@@ -28234,13 +28249,13 @@
         <v>3.59</v>
       </c>
       <c r="AS163" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU163" t="n">
         <v>1.9</v>
       </c>
       <c r="AV163" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
@@ -28507,7 +28522,7 @@
         </is>
       </c>
       <c r="AI165" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ165" t="n">
         <v>0.1084695393759287</v>
@@ -28521,10 +28536,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM165" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN165" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO165" t="n">
         <v>0.75</v>
@@ -28658,7 +28673,7 @@
         <v>0.315</v>
       </c>
       <c r="AI166" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ166" t="n">
         <v>0.1948051948051948</v>
@@ -28672,10 +28687,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM166" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN166" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO166" t="n">
         <v>1.14</v>
@@ -28702,7 +28717,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.96, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.86, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
@@ -28814,7 +28829,7 @@
         <v>0.8554666666666666</v>
       </c>
       <c r="AI167" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ167" t="n">
         <v>0.1477309301577084</v>
@@ -28828,10 +28843,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM167" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="AN167" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="AO167" t="n">
         <v>1.9</v>
@@ -28967,7 +28982,7 @@
         <v>6.185648148148148</v>
       </c>
       <c r="AI168" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ168" t="n">
         <v>0.1678832116788321</v>
@@ -28981,10 +28996,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM168" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN168" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO168" t="n">
         <v>2</v>
@@ -28996,13 +29011,16 @@
         <v>4.94</v>
       </c>
       <c r="AS168" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>4.79</v>
       </c>
       <c r="AU168" t="n">
         <v>2</v>
       </c>
       <c r="AV168" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
@@ -29124,7 +29142,7 @@
         <v>0</v>
       </c>
       <c r="AI169" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ169" t="n">
         <v>0.1084695393759287</v>
@@ -29138,10 +29156,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM169" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN169" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO169" t="n">
         <v>1.05</v>
@@ -29263,7 +29281,7 @@
         </is>
       </c>
       <c r="AI170" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ170" t="n">
         <v>0.1678832116788321</v>
@@ -29277,10 +29295,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM170" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN170" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AO170" t="n">
         <v>1.82</v>
@@ -29417,7 +29435,7 @@
         <v>13.53812636165577</v>
       </c>
       <c r="AI171" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ171" t="n">
         <v>0.1477309301577084</v>
@@ -29431,10 +29449,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM171" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="AN171" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="AO171" t="n">
         <v>1.27</v>
@@ -29564,7 +29582,7 @@
         </is>
       </c>
       <c r="AI172" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ172" t="n">
         <v>0.1948051948051948</v>
@@ -29578,10 +29596,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM172" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN172" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO172" t="n">
         <v>2</v>
@@ -29715,7 +29733,7 @@
         </is>
       </c>
       <c r="AI173" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ173" t="n">
         <v>0.1084695393759287</v>
@@ -29729,10 +29747,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM173" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN173" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO173" t="n">
         <v>1.2</v>
@@ -29866,7 +29884,7 @@
         <v>1.832559241706161</v>
       </c>
       <c r="AI174" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ174" t="n">
         <v>0.1536572622779519</v>
@@ -29880,10 +29898,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM174" t="n">
-        <v>4.7</v>
+        <v>4.38</v>
       </c>
       <c r="AN174" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO174" t="n">
         <v>1.9</v>
@@ -29895,16 +29913,16 @@
         <v>4.75</v>
       </c>
       <c r="AS174" t="n">
-        <v>4.7</v>
+        <v>4.38</v>
       </c>
       <c r="AT174" t="n">
-        <v>4.7</v>
+        <v>4.38</v>
       </c>
       <c r="AU174" t="n">
         <v>1.9</v>
       </c>
       <c r="AV174" t="n">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
@@ -30027,7 +30045,7 @@
         <v>10.53620352250489</v>
       </c>
       <c r="AI175" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ175" t="n">
         <v>0.1084695393759287</v>
@@ -30041,10 +30059,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM175" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN175" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO175" t="n">
         <v>1.6</v>
@@ -30056,13 +30074,13 @@
         <v>2.56</v>
       </c>
       <c r="AS175" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AU175" t="n">
         <v>1.6</v>
       </c>
       <c r="AV175" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
@@ -30169,7 +30187,7 @@
         <v>9.027619047619048</v>
       </c>
       <c r="AI176" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ176" t="n">
         <v>0.1362935553499846</v>
@@ -30183,10 +30201,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM176" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AN176" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AO176" t="n">
         <v>1.9</v>
@@ -30198,16 +30216,16 @@
         <v>4.69</v>
       </c>
       <c r="AS176" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AT176" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AU176" t="n">
         <v>1.9</v>
       </c>
       <c r="AV176" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
@@ -30325,7 +30343,7 @@
         <v>3.039512195121951</v>
       </c>
       <c r="AI177" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ177" t="n">
         <v>0.1477309301577084</v>
@@ -30339,10 +30357,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM177" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="AN177" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="AP177" t="n">
         <v>100</v>
@@ -30472,7 +30490,7 @@
         <v>0.7595818815331009</v>
       </c>
       <c r="AI178" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ178" t="n">
         <v>0.1880733944954129</v>
@@ -30486,10 +30504,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM178" t="n">
-        <v>4.52</v>
+        <v>3.82</v>
       </c>
       <c r="AN178" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="AO178" t="n">
         <v>1.15</v>
@@ -30627,7 +30645,7 @@
         <v>1.519163763066202</v>
       </c>
       <c r="AI179" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ179" t="n">
         <v>0.1880733944954129</v>
@@ -30641,10 +30659,10 @@
         <v>0.1456953642384106</v>
       </c>
       <c r="AM179" t="n">
-        <v>5.31</v>
+        <v>4.51</v>
       </c>
       <c r="AN179" t="n">
-        <v>4.11</v>
+        <v>3.49</v>
       </c>
       <c r="AO179" t="n">
         <v>0.96</v>
@@ -30783,7 +30801,7 @@
         <v>2.900625</v>
       </c>
       <c r="AI180" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ180" t="n">
         <v>0.1477309301577084</v>
@@ -30797,10 +30815,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM180" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="AN180" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="AO180" t="n">
         <v>1</v>
@@ -30812,16 +30830,16 @@
         <v>4.81</v>
       </c>
       <c r="AS180" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="AT180" t="n">
-        <v>4.17</v>
+        <v>3.54</v>
       </c>
       <c r="AU180" t="n">
         <v>1</v>
       </c>
       <c r="AV180" t="n">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
@@ -30830,7 +30848,7 @@
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.54, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
@@ -30936,7 +30954,7 @@
         <v>7.303942307692308</v>
       </c>
       <c r="AI181" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ181" t="n">
         <v>0.1362935553499846</v>
@@ -30950,10 +30968,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM181" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AN181" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AO181" t="n">
         <v>1.9</v>
@@ -30965,16 +30983,16 @@
         <v>4.69</v>
       </c>
       <c r="AS181" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AT181" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AU181" t="n">
         <v>1.9</v>
       </c>
       <c r="AV181" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
@@ -31104,7 +31122,7 @@
         <v>0</v>
       </c>
       <c r="AI182" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ182" t="n">
         <v>0.1641414141414141</v>
@@ -31118,10 +31136,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM182" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN182" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AO182" t="n">
         <v>1.9</v>
@@ -31133,13 +31151,13 @@
         <v>4.46</v>
       </c>
       <c r="AS182" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AU182" t="n">
         <v>1.9</v>
       </c>
       <c r="AV182" t="n">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
@@ -31148,7 +31166,7 @@
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.02, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.68, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
@@ -31250,7 +31268,7 @@
         <v>0</v>
       </c>
       <c r="AI183" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ183" t="n">
         <v>0.1362935553499846</v>
@@ -31264,10 +31282,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM183" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN183" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO183" t="n">
         <v>1.9</v>
@@ -31279,13 +31297,13 @@
         <v>3.36</v>
       </c>
       <c r="AS183" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU183" t="n">
         <v>1.9</v>
       </c>
       <c r="AV183" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
@@ -31392,7 +31410,7 @@
         <v>0</v>
       </c>
       <c r="AI184" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ184" t="n">
         <v>0.1362935553499846</v>
@@ -31406,10 +31424,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM184" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN184" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO184" t="n">
         <v>1.9</v>
@@ -31540,7 +31558,7 @@
         <v>0.921590909090909</v>
       </c>
       <c r="AI185" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ185" t="n">
         <v>0.1678832116788321</v>
@@ -31554,10 +31572,10 @@
         <v>0.05932203389830509</v>
       </c>
       <c r="AM185" t="n">
-        <v>5.14</v>
+        <v>4.79</v>
       </c>
       <c r="AN185" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AP185" t="n">
         <v>100</v>
@@ -31569,7 +31587,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.14, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $4.79, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -31664,7 +31682,7 @@
         </is>
       </c>
       <c r="AI186" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ186" t="n">
         <v>0.1362935553499846</v>
@@ -31678,10 +31696,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM186" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN186" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP186" t="n">
         <v>100</v>
@@ -31791,7 +31809,7 @@
         <v>1.053913043478261</v>
       </c>
       <c r="AI187" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ187" t="n">
         <v>0.1362935553499846</v>
@@ -31805,10 +31823,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM187" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN187" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO187" t="n">
         <v>1.9</v>
@@ -31820,16 +31838,16 @@
         <v>4.33</v>
       </c>
       <c r="AS187" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT187" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU187" t="n">
         <v>1.9</v>
       </c>
       <c r="AV187" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
@@ -31936,7 +31954,7 @@
         <v>16.52615384615385</v>
       </c>
       <c r="AI188" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ188" t="n">
         <v>0.1362935553499846</v>
@@ -31950,10 +31968,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM188" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN188" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO188" t="n">
         <v>1.9</v>
@@ -31965,16 +31983,16 @@
         <v>4.69</v>
       </c>
       <c r="AS188" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT188" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU188" t="n">
         <v>1.9</v>
       </c>
       <c r="AV188" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
@@ -32078,7 +32096,7 @@
         </is>
       </c>
       <c r="AI189" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ189" t="n">
         <v>0.1084695393759287</v>
@@ -32092,10 +32110,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM189" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AN189" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="AO189" t="n">
         <v>1.8</v>
@@ -32107,16 +32125,16 @@
         <v>3.42</v>
       </c>
       <c r="AS189" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AT189" t="n">
-        <v>3.32</v>
+        <v>3.09</v>
       </c>
       <c r="AU189" t="n">
         <v>1.8</v>
       </c>
       <c r="AV189" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
@@ -32220,7 +32238,7 @@
         </is>
       </c>
       <c r="AI190" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ190" t="n">
         <v>0.1362935553499846</v>
@@ -32234,10 +32252,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM190" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN190" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO190" t="n">
         <v>1.57</v>
@@ -32249,13 +32267,13 @@
         <v>3.83</v>
       </c>
       <c r="AS190" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU190" t="n">
         <v>1.57</v>
       </c>
       <c r="AV190" t="n">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
@@ -32359,7 +32377,7 @@
         </is>
       </c>
       <c r="AI191" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ191" t="n">
         <v>0.1948051948051948</v>
@@ -32373,10 +32391,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM191" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN191" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AP191" t="n">
         <v>100</v>
@@ -32504,7 +32522,7 @@
         <v>0.3536363636363636</v>
       </c>
       <c r="AI192" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ192" t="n">
         <v>0.1948051948051948</v>
@@ -32518,10 +32536,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM192" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN192" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AP192" t="n">
         <v>100</v>
@@ -32533,7 +32551,7 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.96, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.86, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -32649,7 +32667,7 @@
         <v>0.002</v>
       </c>
       <c r="AI193" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ193" t="n">
         <v>0.1948051948051948</v>
@@ -32663,10 +32681,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM193" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN193" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AP193" t="n">
         <v>90</v>
@@ -32678,7 +32696,7 @@
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $5.96, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $5.86, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -32788,7 +32806,7 @@
         <v>15.38</v>
       </c>
       <c r="AI194" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ194" t="n">
         <v>0.1362935553499846</v>
@@ -32802,10 +32820,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM194" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN194" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO194" t="n">
         <v>1.9</v>
@@ -32817,16 +32835,16 @@
         <v>4.69</v>
       </c>
       <c r="AS194" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT194" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU194" t="n">
         <v>1.9</v>
       </c>
       <c r="AV194" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
@@ -32956,7 +32974,7 @@
         <v>0</v>
       </c>
       <c r="AI195" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ195" t="n">
         <v>0.2041191936897458</v>
@@ -32970,10 +32988,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM195" t="n">
-        <v>6.25</v>
+        <v>6.14</v>
       </c>
       <c r="AN195" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AO195" t="n">
         <v>1.72</v>
@@ -33100,7 +33118,7 @@
         </is>
       </c>
       <c r="AI196" t="n">
-        <v>30.54</v>
+        <v>29.19</v>
       </c>
       <c r="AJ196" t="n">
         <v>0.1362935553499846</v>
@@ -33114,10 +33132,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM196" t="n">
-        <v>4.16</v>
+        <v>3.98</v>
       </c>
       <c r="AN196" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="AO196" t="n">
         <v>1.9</v>
@@ -33129,13 +33147,13 @@
         <v>3.95</v>
       </c>
       <c r="AS196" t="n">
-        <v>4.16</v>
+        <v>3.98</v>
       </c>
       <c r="AU196" t="n">
         <v>1.9</v>
       </c>
       <c r="AV196" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
@@ -33242,7 +33260,7 @@
         <v>0</v>
       </c>
       <c r="AI197" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ197" t="n">
         <v>0.1362935553499846</v>
@@ -33256,10 +33274,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM197" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN197" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO197" t="n">
         <v>1.9</v>
@@ -33390,7 +33408,7 @@
         <v>1.689130434782609</v>
       </c>
       <c r="AI198" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ198" t="n">
         <v>0.1362935553499846</v>
@@ -33404,10 +33422,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM198" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN198" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO198" t="n">
         <v>1.92</v>
@@ -33419,13 +33437,13 @@
         <v>3.71</v>
       </c>
       <c r="AS198" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU198" t="n">
         <v>1.92</v>
       </c>
       <c r="AV198" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
@@ -33434,7 +33452,7 @@
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $4.17, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.89, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
@@ -33526,7 +33544,7 @@
         </is>
       </c>
       <c r="AI199" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ199" t="n">
         <v>0.1362935553499846</v>
@@ -33540,10 +33558,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM199" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN199" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO199" t="n">
         <v>1.1</v>
@@ -33680,7 +33698,7 @@
         <v>1.662285714285714</v>
       </c>
       <c r="AI200" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ200" t="n">
         <v>0.1362935553499846</v>
@@ -33694,10 +33712,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM200" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN200" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO200" t="n">
         <v>1.9</v>
@@ -33709,13 +33727,13 @@
         <v>3.86</v>
       </c>
       <c r="AS200" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU200" t="n">
         <v>1.9</v>
       </c>
       <c r="AV200" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
@@ -33828,7 +33846,7 @@
         <v>3.841470588235294</v>
       </c>
       <c r="AI201" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ201" t="n">
         <v>0.1948051948051948</v>
@@ -33842,10 +33860,10 @@
         <v>0.06702898550724638</v>
       </c>
       <c r="AM201" t="n">
-        <v>5.96</v>
+        <v>5.86</v>
       </c>
       <c r="AN201" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AO201" t="n">
         <v>2</v>
@@ -33982,7 +34000,7 @@
         <v>12.362</v>
       </c>
       <c r="AI202" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ202" t="n">
         <v>0.1362935553499846</v>
@@ -33996,10 +34014,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM202" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN202" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AO202" t="n">
         <v>2</v>
@@ -34011,16 +34029,16 @@
         <v>4.94</v>
       </c>
       <c r="AS202" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AT202" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AU202" t="n">
         <v>2</v>
       </c>
       <c r="AV202" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
@@ -34135,7 +34153,7 @@
         <v>0</v>
       </c>
       <c r="AI203" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ203" t="n">
         <v>0.1362935553499846</v>
@@ -34149,10 +34167,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM203" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN203" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO203" t="n">
         <v>1.9</v>
@@ -34164,16 +34182,16 @@
         <v>4.52</v>
       </c>
       <c r="AS203" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT203" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU203" t="n">
         <v>1.52</v>
       </c>
       <c r="AV203" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
@@ -34286,7 +34304,7 @@
         <v>0.2460176991150443</v>
       </c>
       <c r="AI204" t="n">
-        <v>24.37</v>
+        <v>21.71</v>
       </c>
       <c r="AJ204" t="n">
         <v>0.1477309301577084</v>
@@ -34300,10 +34318,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM204" t="n">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="AN204" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AP204" t="n">
         <v>100</v>
@@ -34315,7 +34333,7 @@
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $3.60, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.21, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
@@ -34427,7 +34445,7 @@
         <v>0.2353846153846154</v>
       </c>
       <c r="AI205" t="n">
-        <v>24.37</v>
+        <v>21.71</v>
       </c>
       <c r="AJ205" t="n">
         <v>0.1477309301577084</v>
@@ -34441,10 +34459,10 @@
         <v>0.09886246122026887</v>
       </c>
       <c r="AM205" t="n">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="AN205" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AP205" t="n">
         <v>100</v>
@@ -34456,7 +34474,7 @@
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>maintenance: top of search at the ceiling $3.60, no premium — push conditions missing: velocity, ctr, cvr</t>
+          <t>maintenance: top of search at the ceiling $3.21, no premium — push conditions missing: velocity, ctr, cvr</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
@@ -34568,7 +34586,7 @@
         <v>1.071607142857143</v>
       </c>
       <c r="AI206" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ206" t="n">
         <v>0.1362935553499846</v>
@@ -34582,10 +34600,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM206" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN206" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO206" t="n">
         <v>1.9</v>
@@ -34597,16 +34615,16 @@
         <v>4.67</v>
       </c>
       <c r="AS206" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AT206" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AU206" t="n">
         <v>1.52</v>
       </c>
       <c r="AV206" t="n">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
@@ -34719,7 +34737,7 @@
         <v>0</v>
       </c>
       <c r="AI207" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ207" t="n">
         <v>0.1362935553499846</v>
@@ -34733,10 +34751,10 @@
         <v>0.09970188287070694</v>
       </c>
       <c r="AM207" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN207" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AO207" t="n">
         <v>1.71</v>
@@ -34875,7 +34893,7 @@
         <v>0.0375609756097561</v>
       </c>
       <c r="AI208" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ208" t="n">
         <v>0.1362935553499846</v>
@@ -34889,10 +34907,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM208" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN208" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AO208" t="n">
         <v>1.9</v>
@@ -35132,7 +35150,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="AI210" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ210" t="n">
         <v>0.1641414141414141</v>
@@ -35146,10 +35164,10 @@
         <v>0.06</v>
       </c>
       <c r="AM210" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN210" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AP210" t="n">
         <v>56</v>
@@ -35487,7 +35505,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="AI213" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ213" t="n">
         <v>0.1641414141414141</v>
@@ -35501,10 +35519,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM213" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN213" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AP213" t="n">
         <v>56</v>
@@ -35730,7 +35748,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="AI215" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ215" t="n">
         <v>0.1641414141414141</v>
@@ -35744,10 +35762,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM215" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN215" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AP215" t="n">
         <v>56</v>
@@ -35872,7 +35890,7 @@
         <v>0</v>
       </c>
       <c r="AI216" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ216" t="n">
         <v>0.1516393442622951</v>
@@ -35886,10 +35904,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM216" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN216" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP216" t="n">
         <v>90</v>
@@ -36014,7 +36032,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="AI217" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ217" t="n">
         <v>0.1362935553499846</v>
@@ -36028,10 +36046,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM217" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN217" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP217" t="n">
         <v>88</v>
@@ -36156,7 +36174,7 @@
         <v>0.2857142857142857</v>
       </c>
       <c r="AI218" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ218" t="n">
         <v>0.1516393442622951</v>
@@ -36170,10 +36188,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM218" t="n">
-        <v>4.64</v>
+        <v>4.56</v>
       </c>
       <c r="AN218" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AP218" t="n">
         <v>90</v>
@@ -36298,7 +36316,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="AI219" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ219" t="n">
         <v>0.1362935553499846</v>
@@ -36312,10 +36330,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM219" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN219" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP219" t="n">
         <v>88</v>
@@ -36437,7 +36455,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="AI220" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ220" t="n">
         <v>0.1516393442622951</v>
@@ -36451,10 +36469,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM220" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN220" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP220" t="n">
         <v>95</v>
@@ -36576,7 +36594,7 @@
         <v>0.07142857142857142</v>
       </c>
       <c r="AI221" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ221" t="n">
         <v>0.1362935553499846</v>
@@ -36590,10 +36608,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM221" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN221" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP221" t="n">
         <v>88</v>
@@ -36715,7 +36733,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="AI222" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ222" t="n">
         <v>0.1641414141414141</v>
@@ -36729,10 +36747,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM222" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN222" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AP222" t="n">
         <v>62</v>
@@ -36854,7 +36872,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="AI223" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ223" t="n">
         <v>0.1362935553499846</v>
@@ -36868,10 +36886,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM223" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN223" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP223" t="n">
         <v>88</v>
@@ -36996,7 +37014,7 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="AI224" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ224" t="n">
         <v>0.1881390593047035</v>
@@ -37010,10 +37028,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM224" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN224" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AP224" t="n">
         <v>129</v>
@@ -37135,7 +37153,7 @@
         <v>0.07142857142857142</v>
       </c>
       <c r="AI225" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ225" t="n">
         <v>0.1881390593047035</v>
@@ -37149,10 +37167,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM225" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN225" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AP225" t="n">
         <v>139</v>
@@ -37378,7 +37396,7 @@
         <v>0.07142857142857142</v>
       </c>
       <c r="AI227" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ227" t="n">
         <v>0.1516393442622951</v>
@@ -37392,10 +37410,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM227" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN227" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP227" t="n">
         <v>95</v>
@@ -37659,7 +37677,7 @@
         <v>0</v>
       </c>
       <c r="AI229" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ229" t="n">
         <v>0.1881390593047035</v>
@@ -37673,10 +37691,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM229" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN229" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AP229" t="n">
         <v>139</v>
@@ -37798,7 +37816,7 @@
         <v>0.07142857142857142</v>
       </c>
       <c r="AI230" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ230" t="n">
         <v>0.1516393442622951</v>
@@ -37812,10 +37830,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM230" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN230" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP230" t="n">
         <v>95</v>
@@ -37937,7 +37955,7 @@
         <v>0.07142857142857142</v>
       </c>
       <c r="AI231" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ231" t="n">
         <v>0.1362935553499846</v>
@@ -37951,10 +37969,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM231" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN231" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP231" t="n">
         <v>160</v>
@@ -38076,7 +38094,7 @@
         <v>0.07142857142857142</v>
       </c>
       <c r="AI232" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ232" t="n">
         <v>0.1362935553499846</v>
@@ -38090,10 +38108,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM232" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN232" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP232" t="n">
         <v>160</v>
@@ -38215,7 +38233,7 @@
         <v>0</v>
       </c>
       <c r="AI233" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ233" t="n">
         <v>0.1362935553499846</v>
@@ -38229,10 +38247,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM233" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN233" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AP233" t="n">
         <v>130</v>
@@ -38354,7 +38372,7 @@
         <v>0</v>
       </c>
       <c r="AI234" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ234" t="n">
         <v>0.1641414141414141</v>
@@ -38368,10 +38386,10 @@
         <v>0.09803921568627451</v>
       </c>
       <c r="AM234" t="n">
-        <v>5.02</v>
+        <v>4.68</v>
       </c>
       <c r="AN234" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AP234" t="n">
         <v>62</v>
@@ -38493,7 +38511,7 @@
         <v>0</v>
       </c>
       <c r="AI235" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ235" t="n">
         <v>0.1516393442622951</v>
@@ -38507,10 +38525,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM235" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN235" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP235" t="n">
         <v>95</v>
@@ -38908,7 +38926,7 @@
         <v>0</v>
       </c>
       <c r="AI239" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ239" t="n">
         <v>0.1362935553499846</v>
@@ -38922,10 +38940,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM239" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN239" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP239" t="n">
         <v>88</v>
@@ -39031,7 +39049,7 @@
         <v>0</v>
       </c>
       <c r="AI240" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ240" t="n">
         <v>0.1516393442622951</v>
@@ -39045,10 +39063,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM240" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN240" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP240" t="n">
         <v>90</v>
@@ -39154,7 +39172,7 @@
         <v>0</v>
       </c>
       <c r="AI241" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ241" t="n">
         <v>0.1881390593047035</v>
@@ -39168,10 +39186,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM241" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN241" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AP241" t="n">
         <v>154</v>
@@ -39275,7 +39293,7 @@
         <v>0</v>
       </c>
       <c r="AI242" t="n">
-        <v>34.87</v>
+        <v>27.58</v>
       </c>
       <c r="AJ242" t="n">
         <v>0.1362935553499846</v>
@@ -39289,10 +39307,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM242" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="AN242" t="n">
-        <v>3.69</v>
+        <v>2.92</v>
       </c>
       <c r="AP242" t="n">
         <v>0</v>
@@ -39398,7 +39416,7 @@
         <v>0</v>
       </c>
       <c r="AI243" t="n">
-        <v>35.16</v>
+        <v>26.64</v>
       </c>
       <c r="AJ243" t="n">
         <v>0.1362935553499846</v>
@@ -39412,10 +39430,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM243" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
       <c r="AN243" t="n">
-        <v>3.72</v>
+        <v>2.82</v>
       </c>
       <c r="AP243" t="n">
         <v>0</v>
@@ -39521,7 +39539,7 @@
         <v>0</v>
       </c>
       <c r="AI244" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ244" t="n">
         <v>0.1362935553499846</v>
@@ -39535,10 +39553,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM244" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN244" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP244" t="n">
         <v>80</v>
@@ -39644,7 +39662,7 @@
         <v>0</v>
       </c>
       <c r="AI245" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ245" t="n">
         <v>0.1362935553499846</v>
@@ -39658,10 +39676,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM245" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN245" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP245" t="n">
         <v>88</v>
@@ -39767,7 +39785,7 @@
         <v>0</v>
       </c>
       <c r="AI246" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ246" t="n">
         <v>0.1362935553499846</v>
@@ -39781,10 +39799,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM246" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN246" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP246" t="n">
         <v>88</v>
@@ -39890,7 +39908,7 @@
         <v>0</v>
       </c>
       <c r="AI247" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ247" t="n">
         <v>0.1362935553499846</v>
@@ -39904,10 +39922,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM247" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN247" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP247" t="n">
         <v>88</v>
@@ -40013,7 +40031,7 @@
         <v>0</v>
       </c>
       <c r="AI248" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ248" t="n">
         <v>0.1362935553499846</v>
@@ -40027,10 +40045,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM248" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN248" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP248" t="n">
         <v>88</v>
@@ -40225,7 +40243,7 @@
         <v>0</v>
       </c>
       <c r="AI250" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ250" t="n">
         <v>0.1516393442622951</v>
@@ -40239,10 +40257,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM250" t="n">
-        <v>4.64</v>
+        <v>4.56</v>
       </c>
       <c r="AN250" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="AP250" t="n">
         <v>95</v>
@@ -40352,7 +40370,7 @@
         <v>0</v>
       </c>
       <c r="AI251" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ251" t="n">
         <v>0.1362935553499846</v>
@@ -40366,10 +40384,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM251" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN251" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP251" t="n">
         <v>88</v>
@@ -40475,7 +40493,7 @@
         <v>0</v>
       </c>
       <c r="AI252" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ252" t="n">
         <v>0.1881390593047035</v>
@@ -40489,10 +40507,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM252" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN252" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AP252" t="n">
         <v>154</v>
@@ -40691,7 +40709,7 @@
         <v>0</v>
       </c>
       <c r="AI254" t="n">
-        <v>24.04</v>
+        <v>20.31</v>
       </c>
       <c r="AJ254" t="n">
         <v>0.1362935553499846</v>
@@ -40705,10 +40723,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM254" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="AN254" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="AP254" t="n">
         <v>70</v>
@@ -40814,7 +40832,7 @@
         <v>0</v>
       </c>
       <c r="AI255" t="n">
-        <v>34.87</v>
+        <v>27.58</v>
       </c>
       <c r="AJ255" t="n">
         <v>0.1362935553499846</v>
@@ -40828,10 +40846,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM255" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="AN255" t="n">
-        <v>3.69</v>
+        <v>2.92</v>
       </c>
       <c r="AP255" t="n">
         <v>0</v>
@@ -41027,7 +41045,7 @@
         <v>0</v>
       </c>
       <c r="AI257" t="n">
-        <v>28.21</v>
+        <v>23.96</v>
       </c>
       <c r="AJ257" t="n">
         <v>0.1362935553499846</v>
@@ -41041,10 +41059,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM257" t="n">
-        <v>3.84</v>
+        <v>3.27</v>
       </c>
       <c r="AN257" t="n">
-        <v>2.98</v>
+        <v>2.53</v>
       </c>
       <c r="AP257" t="n">
         <v>0</v>
@@ -41150,7 +41168,7 @@
         <v>0</v>
       </c>
       <c r="AI258" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ258" t="n">
         <v>0.1362935553499846</v>
@@ -41164,10 +41182,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM258" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN258" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP258" t="n">
         <v>88</v>
@@ -41273,7 +41291,7 @@
         <v>0</v>
       </c>
       <c r="AI259" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ259" t="n">
         <v>0.1362935553499846</v>
@@ -41287,10 +41305,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM259" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN259" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP259" t="n">
         <v>88</v>
@@ -41494,7 +41512,7 @@
         <v>0</v>
       </c>
       <c r="AI261" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ261" t="n">
         <v>0.1362935553499846</v>
@@ -41508,10 +41526,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM261" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="AN261" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="AP261" t="n">
         <v>50</v>
@@ -41617,7 +41635,7 @@
         <v>0</v>
       </c>
       <c r="AI262" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ262" t="n">
         <v>0.1362935553499846</v>
@@ -41631,10 +41649,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM262" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN262" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AP262" t="n">
         <v>0</v>
@@ -41922,7 +41940,7 @@
         <v>0</v>
       </c>
       <c r="AI265" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ265" t="n">
         <v>0.1362935553499846</v>
@@ -41936,10 +41954,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM265" t="n">
-        <v>4.17</v>
+        <v>3.89</v>
       </c>
       <c r="AN265" t="n">
-        <v>3.24</v>
+        <v>3.02</v>
       </c>
       <c r="AP265" t="n">
         <v>20</v>
@@ -42045,7 +42063,7 @@
         <v>0</v>
       </c>
       <c r="AI266" t="n">
-        <v>34.87</v>
+        <v>27.58</v>
       </c>
       <c r="AJ266" t="n">
         <v>0.1362935553499846</v>
@@ -42059,10 +42077,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM266" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="AN266" t="n">
-        <v>3.69</v>
+        <v>2.92</v>
       </c>
       <c r="AP266" t="n">
         <v>83</v>
@@ -42172,7 +42190,7 @@
         <v>0</v>
       </c>
       <c r="AI267" t="n">
-        <v>30.62</v>
+        <v>30.09</v>
       </c>
       <c r="AJ267" t="n">
         <v>0.1881390593047035</v>
@@ -42186,10 +42204,10 @@
         <v>0.1098712446351931</v>
       </c>
       <c r="AM267" t="n">
-        <v>5.76</v>
+        <v>5.66</v>
       </c>
       <c r="AN267" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AP267" t="n">
         <v>154</v>
@@ -42293,7 +42311,7 @@
         <v>0</v>
       </c>
       <c r="AI268" t="n">
-        <v>30.67</v>
+        <v>28.7</v>
       </c>
       <c r="AJ268" t="n">
         <v>0.1362935553499846</v>
@@ -42307,10 +42325,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM268" t="n">
-        <v>4.18</v>
+        <v>3.91</v>
       </c>
       <c r="AN268" t="n">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="AP268" t="n">
         <v>50</v>
@@ -42629,7 +42647,7 @@
         <v>0</v>
       </c>
       <c r="AI271" t="n">
-        <v>30.59</v>
+        <v>28.52</v>
       </c>
       <c r="AJ271" t="n">
         <v>0.1516393442622951</v>
@@ -42643,10 +42661,10 @@
         <v>0.09178743961352658</v>
       </c>
       <c r="AM271" t="n">
-        <v>4.64</v>
+        <v>4.32</v>
       </c>
       <c r="AN271" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AP271" t="n">
         <v>95</v>
@@ -42752,7 +42770,7 @@
         <v>0</v>
       </c>
       <c r="AI272" t="n">
-        <v>34.95</v>
+        <v>25.02</v>
       </c>
       <c r="AJ272" t="n">
         <v>0.1362935553499846</v>
@@ -42766,10 +42784,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM272" t="n">
-        <v>4.76</v>
+        <v>3.41</v>
       </c>
       <c r="AN272" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="AP272" t="n">
         <v>62</v>
@@ -42879,7 +42897,7 @@
         <v>0</v>
       </c>
       <c r="AI273" t="n">
-        <v>34.95</v>
+        <v>25.02</v>
       </c>
       <c r="AJ273" t="n">
         <v>0.1436588696533192</v>
@@ -42893,10 +42911,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM273" t="n">
-        <v>5.02</v>
+        <v>3.59</v>
       </c>
       <c r="AN273" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="AP273" t="n">
         <v>0</v>
@@ -43085,7 +43103,7 @@
         <v>0</v>
       </c>
       <c r="AI275" t="n">
-        <v>24.51</v>
+        <v>17.59</v>
       </c>
       <c r="AJ275" t="n">
         <v>0.1362935553499846</v>
@@ -43099,10 +43117,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM275" t="n">
-        <v>3.34</v>
+        <v>2.4</v>
       </c>
       <c r="AN275" t="n">
-        <v>2.59</v>
+        <v>1.86</v>
       </c>
       <c r="AP275" t="n">
         <v>50</v>
@@ -43202,7 +43220,7 @@
         <v>0</v>
       </c>
       <c r="AI276" t="n">
-        <v>35.16</v>
+        <v>26.64</v>
       </c>
       <c r="AJ276" t="n">
         <v>0.1362935553499846</v>
@@ -43216,10 +43234,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM276" t="n">
-        <v>4.79</v>
+        <v>3.63</v>
       </c>
       <c r="AN276" t="n">
-        <v>3.72</v>
+        <v>2.82</v>
       </c>
       <c r="AP276" t="n">
         <v>0</v>
@@ -43411,7 +43429,7 @@
         <v>0</v>
       </c>
       <c r="AI278" t="n">
-        <v>34.87</v>
+        <v>27.58</v>
       </c>
       <c r="AJ278" t="n">
         <v>0.1362935553499846</v>
@@ -43425,10 +43443,10 @@
         <v>0.1057754704737184</v>
       </c>
       <c r="AM278" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="AN278" t="n">
-        <v>3.69</v>
+        <v>2.92</v>
       </c>
       <c r="AP278" t="n">
         <v>0</v>

--- a/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
+++ b/docs/DBS4_Campaign_Review_20260928-9e6e6bb5.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>OBJECTIVE: tagged Ranking but a Broad campaign is Discovery by the standard | SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; it should advertise an LTSF SKU (list pending) | MISSING: over its ceiling and the run does not bring the base down | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $3 in 30d) — “cooling sheets queen” 1</t>
+          <t>OBJECTIVE: tagged Ranking but a Broad campaign is Discovery by the standard | SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; King has no LTSF child today — advertise a non-White child | MISSING: over its ceiling and the run does not bring the base down | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $3 in 30d) — “cooling sheets queen” 1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -43736,7 +43736,7 @@
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 3 exact ranking terms (20 clicks, $36 in 30d) — “bamboo sheets” 13, “bamboo sheets queen size” 5, “cooling sheets queen” 2</t>
+          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; King has no LTSF child today — advertise a non-White child | SEARCH TERM: buys 3 exact ranking terms (20 clicks, $36 in 30d) — “bamboo sheets” 13, “bamboo sheets queen size” 5, “cooling sheets queen” 2</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
@@ -43852,12 +43852,12 @@
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-QUEEN-WHITE; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 4 exact ranking terms (31 clicks, $86 in 30d) — “bamboo sheets queen size” 19, “bamboo sheets” 9, “bamboo cooling sheets” 2, “bamboo sheets deep pocket” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-QUEEN-WHITE; the Queen LTSF SKU is BAMBOO-QUEEN-LIGHTOLIVE (10 sold in 30 days, 113 Available, 174 days) | SEARCH TERM: buys 4 exact ranking terms (31 clicks, $86 in 30d) — “bamboo sheets queen size” 19, “bamboo sheets” 9, “bamboo cooling sheets” 2, “bamboo sheets deep pocket” 1</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-QUEEN-LIGHTOLIVE | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -43968,7 +43968,7 @@
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; it should advertise an LTSF SKU (list pending) | MISSING: over its ceiling and the run does not bring the base down | SEARCH TERM: buys 2 exact ranking terms (2 clicks, $3 in 30d) — “bamboo sheets king” 1, “bamboo sheets king size” 1</t>
+          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; King has no LTSF child today — advertise a non-White child | MISSING: over its ceiling and the run does not bring the base down | SEARCH TERM: buys 2 exact ranking terms (2 clicks, $3 in 30d) — “bamboo sheets king” 1, “bamboo sheets king size” 1</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
@@ -44084,12 +44084,12 @@
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-CALIFKING-WHITE; it should advertise an LTSF SKU (list pending) | SEARCH TERM: buys 3 exact ranking terms (5 clicks, $11 in 30d) — “bamboo sheets” 2, “california king bamboo sheets” 2, “bamboo sheets king size” 1</t>
+          <t>SKU: Broad campaign advertises BAMBOO-CALIFKING-WHITE; the California King LTSF SKU is BAMBOO-CALIFKING-GREY (7 sold in 30 days, 56 Available, 156 days) | SEARCH TERM: buys 3 exact ranking terms (5 clicks, $11 in 30d) — “bamboo sheets” 2, “california king bamboo sheets” 2, “bamboo sheets king size” 1</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
+          <t>advertise BAMBOO-CALIFKING-GREY | negative-exact the ranking terms it buys (they belong to their exact campaigns)</t>
         </is>
       </c>
     </row>
@@ -44200,7 +44200,7 @@
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; it should advertise an LTSF SKU (list pending) | RUN: cuts a campaign that is inside its ceiling (bid 1.3→1.17, bid 1.6→1.44) — hold instead | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $2 in 30d) — “bamboo sheets california king” 1</t>
+          <t>SKU: Broad campaign advertises the White ranking SKU BAMBOO-KING-WHITE; King has no LTSF child today — advertise a non-White child | RUN: cuts a campaign that is inside its ceiling (bid 1.3→1.17, bid 1.6→1.44) — hold instead | SEARCH TERM: buys 1 exact ranking terms (1 clicks, $2 in 30d) — “bamboo sheets california king” 1</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
@@ -44314,8 +44314,16 @@
           <t>negatives 40 term(s)→131 term(s)</t>
         </is>
       </c>
-      <c r="AZ284" t="inlineStr"/>
-      <c r="BA284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>SKU: Auto campaign advertises BAMBOO-TWIN-NAVYBLUE; the Twin LTSF SKU is BAMBOO-TWIN-BURGUNDY-NEW (5 sold in 30 days, 133 Available, 665 days)</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>advertise BAMBOO-TWIN-BURGUNDY-NEW</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -44424,7 +44432,7 @@
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>SKU: Auto campaign advertises the White ranking SKU BAMBOO-KING-WHITE; it should advertise an LTSF SKU (list pending)</t>
+          <t>SKU: Auto campaign advertises the White ranking SKU BAMBOO-KING-WHITE; King has no LTSF child today — advertise a non-White child</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr"/>
